--- a/atom01_pcb/Roboto_Usb2Can/02_Assembly/PickAndPlace_HUB_USBTOCAN_V1_0.xlsx
+++ b/atom01_pcb/Roboto_Usb2Can/02_Assembly/PickAndPlace_HUB_USBTOCAN_V1_0.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_HUB_USBTOCAN_V1_0" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_Roboto_uUsb2Can_V1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="545">
   <si>
     <t>Designator</t>
   </si>
@@ -58,1401 +58,1578 @@
     <t>Name</t>
   </si>
   <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>CL05B104KB54PNC</t>
+  </si>
+  <si>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>99.822mm</t>
+  </si>
+  <si>
+    <t>-49.657mm</t>
+  </si>
+  <si>
+    <t>99.277mm</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>100.076mm</t>
+  </si>
+  <si>
+    <t>-57.658mm</t>
+  </si>
+  <si>
+    <t>99.531mm</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>100.05mm</t>
+  </si>
+  <si>
+    <t>-58.775mm</t>
+  </si>
+  <si>
+    <t>99.505mm</t>
+  </si>
+  <si>
+    <t>C51</t>
+  </si>
+  <si>
+    <t>108.712mm</t>
+  </si>
+  <si>
+    <t>-58.801mm</t>
+  </si>
+  <si>
+    <t>109.257mm</t>
+  </si>
+  <si>
+    <t>C42</t>
+  </si>
+  <si>
+    <t>-48.514mm</t>
+  </si>
+  <si>
+    <t>108.167mm</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>100.293mm</t>
+  </si>
+  <si>
+    <t>-46.826mm</t>
+  </si>
+  <si>
+    <t>-46.281mm</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>-57.785mm</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CL05A105KA5NQNC</t>
+  </si>
+  <si>
+    <t>68.834mm</t>
+  </si>
+  <si>
+    <t>-61.341mm</t>
+  </si>
+  <si>
+    <t>69.379mm</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>86.524mm</t>
+  </si>
+  <si>
+    <t>-65.871mm</t>
+  </si>
+  <si>
+    <t>-66.416mm</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>86.487mm</t>
+  </si>
+  <si>
+    <t>-63.5mm</t>
+  </si>
+  <si>
+    <t>-64.045mm</t>
+  </si>
+  <si>
     <t>C2</t>
   </si>
   <si>
-    <t>CL05B104KB54PNC</t>
-  </si>
-  <si>
-    <t>C0402</t>
-  </si>
-  <si>
-    <t>99.822mm</t>
-  </si>
-  <si>
-    <t>-49.657mm</t>
-  </si>
-  <si>
-    <t>99.277mm</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>100nF</t>
+    <t>108.204mm</t>
+  </si>
+  <si>
+    <t>-81.28mm</t>
+  </si>
+  <si>
+    <t>-80.735mm</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>-61.087mm</t>
+  </si>
+  <si>
+    <t>-60.542mm</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>88.9mm</t>
+  </si>
+  <si>
+    <t>88.355mm</t>
+  </si>
+  <si>
+    <t>C43</t>
+  </si>
+  <si>
+    <t>97.626mm</t>
+  </si>
+  <si>
+    <t>-58.711mm</t>
+  </si>
+  <si>
+    <t>98.171mm</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>C45</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>97.536mm</t>
+  </si>
+  <si>
+    <t>96.991mm</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>97.663mm</t>
+  </si>
+  <si>
+    <t>98.208mm</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>-48.768mm</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>CC0603JRNPO9BN120</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>78.486mm</t>
+  </si>
+  <si>
+    <t>-43.942mm</t>
+  </si>
+  <si>
+    <t>-43.242mm</t>
+  </si>
+  <si>
+    <t>12pF</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>-41.021mm</t>
+  </si>
+  <si>
+    <t>-41.721mm</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>XL2EL89CSI-111YLC-12M</t>
+  </si>
+  <si>
+    <t>CRYSTAL-SMD_4P-L3.2-W2.5-BL</t>
+  </si>
+  <si>
+    <t>75.819mm</t>
+  </si>
+  <si>
+    <t>-42.291mm</t>
+  </si>
+  <si>
+    <t>74.969mm</t>
+  </si>
+  <si>
+    <t>-41.191mm</t>
+  </si>
+  <si>
+    <t>12MHz</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>88.011mm</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>96.938mm</t>
+  </si>
+  <si>
+    <t>-81.19mm</t>
+  </si>
+  <si>
+    <t>-80.645mm</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>-65.913mm</t>
+  </si>
+  <si>
+    <t>-66.458mm</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>86.614mm</t>
+  </si>
+  <si>
+    <t>87.159mm</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>77.343mm</t>
+  </si>
+  <si>
+    <t>-58.928mm</t>
+  </si>
+  <si>
+    <t>76.798mm</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>77.47mm</t>
+  </si>
+  <si>
+    <t>76.925mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>-50.038mm</t>
+  </si>
+  <si>
+    <t>85.942mm</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>77.433mm</t>
+  </si>
+  <si>
+    <t>-48.551mm</t>
+  </si>
+  <si>
+    <t>76.888mm</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>85.725mm</t>
+  </si>
+  <si>
+    <t>-80.899mm</t>
+  </si>
+  <si>
+    <t>-80.354mm</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>74.549mm</t>
+  </si>
+  <si>
+    <t>75.094mm</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>74.575mm</t>
+  </si>
+  <si>
+    <t>-57.759mm</t>
+  </si>
+  <si>
+    <t>75.121mm</t>
+  </si>
+  <si>
+    <t>C47</t>
+  </si>
+  <si>
+    <t>66.003mm</t>
+  </si>
+  <si>
+    <t>65.458mm</t>
+  </si>
+  <si>
+    <t>C48</t>
+  </si>
+  <si>
+    <t>66.002mm</t>
+  </si>
+  <si>
+    <t>-49.62mm</t>
+  </si>
+  <si>
+    <t>65.457mm</t>
+  </si>
+  <si>
+    <t>C41</t>
+  </si>
+  <si>
+    <t>74.676mm</t>
+  </si>
+  <si>
+    <t>-49.784mm</t>
+  </si>
+  <si>
+    <t>74.131mm</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>65.405mm</t>
+  </si>
+  <si>
+    <t>-58.42mm</t>
+  </si>
+  <si>
+    <t>-58.965mm</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>66.548mm</t>
   </si>
   <si>
     <t>C3</t>
   </si>
   <si>
-    <t>100.076mm</t>
-  </si>
-  <si>
-    <t>-57.658mm</t>
-  </si>
-  <si>
-    <t>99.531mm</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>100.05mm</t>
-  </si>
-  <si>
-    <t>-58.775mm</t>
-  </si>
-  <si>
-    <t>99.505mm</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>108.712mm</t>
-  </si>
-  <si>
-    <t>-58.801mm</t>
-  </si>
-  <si>
-    <t>109.257mm</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>-48.514mm</t>
-  </si>
-  <si>
-    <t>108.167mm</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>100.293mm</t>
-  </si>
-  <si>
-    <t>-46.826mm</t>
-  </si>
-  <si>
-    <t>-46.281mm</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>-57.785mm</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>CL05A105KA5NQNC</t>
-  </si>
-  <si>
-    <t>68.834mm</t>
-  </si>
-  <si>
-    <t>-61.341mm</t>
-  </si>
-  <si>
-    <t>69.379mm</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C10</t>
+    <t>74.967mm</t>
+  </si>
+  <si>
+    <t>-80.936mm</t>
+  </si>
+  <si>
+    <t>-80.391mm</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>ESDA6V1L_C587141</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
+  </si>
+  <si>
+    <t>103.759mm</t>
+  </si>
+  <si>
+    <t>-81.534mm</t>
+  </si>
+  <si>
+    <t>104.709mm</t>
+  </si>
+  <si>
+    <t>-80.534mm</t>
+  </si>
+  <si>
+    <t>ESDA6V1L</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>92.456mm</t>
+  </si>
+  <si>
+    <t>93.406mm</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>81.28mm</t>
+  </si>
+  <si>
+    <t>82.23mm</t>
+  </si>
+  <si>
+    <t>-80.28mm</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>70.485mm</t>
+  </si>
+  <si>
+    <t>71.435mm</t>
+  </si>
+  <si>
+    <t>LED3</t>
+  </si>
+  <si>
+    <t>SZYY0603B</t>
+  </si>
+  <si>
+    <t>LED0603-R-RD_BLUE</t>
+  </si>
+  <si>
+    <t>96.774mm</t>
+  </si>
+  <si>
+    <t>-33.02mm</t>
+  </si>
+  <si>
+    <t>-33.871mm</t>
+  </si>
+  <si>
+    <t>LED4</t>
+  </si>
+  <si>
+    <t>SZYY0603G</t>
+  </si>
+  <si>
+    <t>LED0603-R-RD_GREEN</t>
+  </si>
+  <si>
+    <t>98.806mm</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>94.742mm</t>
+  </si>
+  <si>
+    <t>LED6</t>
+  </si>
+  <si>
+    <t>89.916mm</t>
+  </si>
+  <si>
+    <t>LED7</t>
+  </si>
+  <si>
+    <t>91.821mm</t>
+  </si>
+  <si>
+    <t>LED5</t>
+  </si>
+  <si>
+    <t>87.884mm</t>
+  </si>
+  <si>
+    <t>LED9</t>
+  </si>
+  <si>
+    <t>82.69mm</t>
+  </si>
+  <si>
+    <t>-32.994mm</t>
+  </si>
+  <si>
+    <t>-33.845mm</t>
+  </si>
+  <si>
+    <t>LED10</t>
+  </si>
+  <si>
+    <t>84.722mm</t>
+  </si>
+  <si>
+    <t>LED8</t>
+  </si>
+  <si>
+    <t>80.658mm</t>
+  </si>
+  <si>
+    <t>LED12</t>
+  </si>
+  <si>
+    <t>75.324mm</t>
+  </si>
+  <si>
+    <t>-33.007mm</t>
+  </si>
+  <si>
+    <t>-33.858mm</t>
+  </si>
+  <si>
+    <t>LED13</t>
+  </si>
+  <si>
+    <t>LED11</t>
+  </si>
+  <si>
+    <t>73.292mm</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>0402WGF1002TCE</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>108.839mm</t>
+  </si>
+  <si>
+    <t>109.272mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>R27</t>
+  </si>
+  <si>
+    <t>105.156mm</t>
+  </si>
+  <si>
+    <t>-59.436mm</t>
+  </si>
+  <si>
+    <t>104.723mm</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>0603WAF1200T5E</t>
+  </si>
+  <si>
+    <t>R0603_1</t>
+  </si>
+  <si>
+    <t>101.473mm</t>
+  </si>
+  <si>
+    <t>-81.661mm</t>
+  </si>
+  <si>
+    <t>-82.414mm</t>
+  </si>
+  <si>
+    <t>120Ω</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>0603WAF0000T5E</t>
+  </si>
+  <si>
+    <t>100.584mm</t>
+  </si>
+  <si>
+    <t>-36.195mm</t>
+  </si>
+  <si>
+    <t>-35.442mm</t>
+  </si>
+  <si>
+    <t>0Ω</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>0603WAF1001T5E</t>
+  </si>
+  <si>
+    <t>92.583mm</t>
+  </si>
+  <si>
+    <t>-37.973mm</t>
+  </si>
+  <si>
+    <t>-38.726mm</t>
+  </si>
+  <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>94.234mm</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>95.898mm</t>
+  </si>
+  <si>
+    <t>-37.947mm</t>
+  </si>
+  <si>
+    <t>-38.7mm</t>
+  </si>
+  <si>
+    <t>R28</t>
+  </si>
+  <si>
+    <t>98.096mm</t>
+  </si>
+  <si>
+    <t>R25</t>
+  </si>
+  <si>
+    <t>93.98mm</t>
+  </si>
+  <si>
+    <t>-59.309mm</t>
+  </si>
+  <si>
+    <t>93.547mm</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>90.17mm</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>87.757mm</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>89.408mm</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>91.059mm</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>-49.022mm</t>
+  </si>
+  <si>
+    <t>87.047mm</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>82.677mm</t>
+  </si>
+  <si>
+    <t>82.244mm</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>78.994mm</t>
+  </si>
+  <si>
+    <t>-81.788mm</t>
+  </si>
+  <si>
+    <t>-82.541mm</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>79.375mm</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>81.026mm</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>82.423mm</t>
+  </si>
+  <si>
+    <t>R29</t>
+  </si>
+  <si>
+    <t>74.93mm</t>
+  </si>
+  <si>
+    <t>75.363mm</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>70.866mm</t>
+  </si>
+  <si>
+    <t>70.433mm</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>68.199mm</t>
+  </si>
+  <si>
+    <t>-82.169mm</t>
+  </si>
+  <si>
+    <t>-82.922mm</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>74.295mm</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>75.946mm</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>77.597mm</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>VPT85BB-01A</t>
+  </si>
+  <si>
+    <t>XFMR-SMD_L7.5-W6.7-P2.54-LS7.7-BL</t>
+  </si>
+  <si>
+    <t>75.692mm</t>
+  </si>
+  <si>
+    <t>71.842mm</t>
+  </si>
+  <si>
+    <t>-60.96mm</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>98.933mm</t>
+  </si>
+  <si>
+    <t>102.783mm</t>
+  </si>
+  <si>
+    <t>-66.04mm</t>
+  </si>
+  <si>
+    <t>U18</t>
+  </si>
+  <si>
+    <t>STM32G431C8T6</t>
+  </si>
+  <si>
+    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
+  </si>
+  <si>
+    <t>104.394mm</t>
+  </si>
+  <si>
+    <t>-53.594mm</t>
+  </si>
+  <si>
+    <t>108.644mm</t>
+  </si>
+  <si>
+    <t>-56.344mm</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>VPS8505</t>
+  </si>
+  <si>
+    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>68.326mm</t>
+  </si>
+  <si>
+    <t>69.676mm</t>
+  </si>
+  <si>
+    <t>-64.45mm</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>DSK36_C22466353</t>
+  </si>
+  <si>
+    <t>SOD-123FL_L2.8-W1.9-LS3.7-RD</t>
+  </si>
+  <si>
+    <t>83.312mm</t>
+  </si>
+  <si>
+    <t>85.012mm</t>
+  </si>
+  <si>
+    <t>DSK36</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>83.439mm</t>
+  </si>
+  <si>
+    <t>-66.294mm</t>
+  </si>
+  <si>
+    <t>85.139mm</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>TPS76350DBVR-TP</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L3.0-W1.6-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>82.162mm</t>
+  </si>
+  <si>
+    <t>-62.55mm</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>ISO1050DWR</t>
+  </si>
+  <si>
+    <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
+  </si>
+  <si>
+    <t>-73.66mm</t>
+  </si>
+  <si>
+    <t>-68.91mm</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>93.218mm</t>
+  </si>
+  <si>
+    <t>97.468mm</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>107.061mm</t>
+  </si>
+  <si>
+    <t>105.711mm</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>89.359mm</t>
+  </si>
+  <si>
+    <t>U15</t>
+  </si>
+  <si>
+    <t>91.186mm</t>
+  </si>
+  <si>
+    <t>-60.833mm</t>
+  </si>
+  <si>
+    <t>89.486mm</t>
+  </si>
+  <si>
+    <t>U13</t>
+  </si>
+  <si>
+    <t>92.336mm</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>96.901mm</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>81.915mm</t>
+  </si>
+  <si>
+    <t>-53.721mm</t>
+  </si>
+  <si>
+    <t>86.165mm</t>
+  </si>
+  <si>
+    <t>-56.471mm</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>CGA0603X5R226M160JT</t>
+  </si>
+  <si>
+    <t>65.532mm</t>
+  </si>
+  <si>
+    <t>-46.355mm</t>
+  </si>
+  <si>
+    <t>-47.055mm</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>SI2301_C2891731</t>
+  </si>
+  <si>
+    <t>74.168mm</t>
+  </si>
+  <si>
+    <t>-46.228mm</t>
+  </si>
+  <si>
+    <t>73.168mm</t>
+  </si>
+  <si>
+    <t>-45.278mm</t>
+  </si>
+  <si>
+    <t>SI2301</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>81.534mm</t>
+  </si>
+  <si>
+    <t>-73.533mm</t>
+  </si>
+  <si>
+    <t>85.979mm</t>
+  </si>
+  <si>
+    <t>-68.783mm</t>
+  </si>
+  <si>
+    <t>U17</t>
+  </si>
+  <si>
+    <t>70.231mm</t>
+  </si>
+  <si>
+    <t>74.481mm</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>SS8050_C916392</t>
+  </si>
+  <si>
+    <t>69.596mm</t>
+  </si>
+  <si>
+    <t>68.596mm</t>
+  </si>
+  <si>
+    <t>-45.405mm</t>
+  </si>
+  <si>
+    <t>SS8050</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>0603WAF1004T5E</t>
+  </si>
+  <si>
+    <t>67.183mm</t>
+  </si>
+  <si>
+    <t>-45.602mm</t>
+  </si>
+  <si>
+    <t>1MΩ</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>RCA03100KJLF</t>
+  </si>
+  <si>
+    <t>72.009mm</t>
+  </si>
+  <si>
+    <t>-45.475mm</t>
+  </si>
+  <si>
+    <t>100kΩ</t>
+  </si>
+  <si>
+    <t>TP7</t>
+  </si>
+  <si>
+    <t>Test-Point</t>
+  </si>
+  <si>
+    <t>Test-Point-0.5mm</t>
+  </si>
+  <si>
+    <t>69.5mm</t>
+  </si>
+  <si>
+    <t>-56.238mm</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>TP10</t>
+  </si>
+  <si>
+    <t>70.75mm</t>
+  </si>
+  <si>
+    <t>TP14</t>
+  </si>
+  <si>
+    <t>67mm</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>TP16</t>
+  </si>
+  <si>
+    <t>68.25mm</t>
+  </si>
+  <si>
+    <t>TP6</t>
+  </si>
+  <si>
+    <t>92.5mm</t>
+  </si>
+  <si>
+    <t>-55.785mm</t>
+  </si>
+  <si>
+    <t>TP9</t>
+  </si>
+  <si>
+    <t>93.75mm</t>
+  </si>
+  <si>
+    <t>TP12</t>
+  </si>
+  <si>
+    <t>90mm</t>
+  </si>
+  <si>
+    <t>TP15</t>
+  </si>
+  <si>
+    <t>91.25mm</t>
+  </si>
+  <si>
+    <t>TP5</t>
+  </si>
+  <si>
+    <t>103.5mm</t>
+  </si>
+  <si>
+    <t>-56.023mm</t>
+  </si>
+  <si>
+    <t>TP8</t>
+  </si>
+  <si>
+    <t>104.75mm</t>
+  </si>
+  <si>
+    <t>TP11</t>
+  </si>
+  <si>
+    <t>101mm</t>
+  </si>
+  <si>
+    <t>TP13</t>
+  </si>
+  <si>
+    <t>102.25mm</t>
+  </si>
+  <si>
+    <t>TP1</t>
+  </si>
+  <si>
+    <t>81mm</t>
+  </si>
+  <si>
+    <t>-56.397mm</t>
+  </si>
+  <si>
+    <t>TP2</t>
+  </si>
+  <si>
+    <t>82.25mm</t>
+  </si>
+  <si>
+    <t>TP3</t>
+  </si>
+  <si>
+    <t>78.5mm</t>
+  </si>
+  <si>
+    <t>TP4</t>
+  </si>
+  <si>
+    <t>79.75mm</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>108.56mm</t>
+  </si>
+  <si>
+    <t>-65.636mm</t>
+  </si>
+  <si>
+    <t>108.015mm</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>105.918mm</t>
+  </si>
+  <si>
+    <t>-65.659mm</t>
+  </si>
+  <si>
+    <t>105.373mm</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>68.961mm</t>
+  </si>
+  <si>
+    <t>-65.786mm</t>
+  </si>
+  <si>
+    <t>69.506mm</t>
   </si>
   <si>
     <t>C14</t>
   </si>
   <si>
-    <t>86.524mm</t>
-  </si>
-  <si>
-    <t>-65.871mm</t>
-  </si>
-  <si>
-    <t>-66.416mm</t>
+    <t>66.294mm</t>
+  </si>
+  <si>
+    <t>65.749mm</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
+    <t>SM02B-GHS-TB(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-SMD_SM02B-GHS-TB-LF-SN</t>
+  </si>
+  <si>
+    <t>-86.995mm</t>
+  </si>
+  <si>
+    <t>98.181mm</t>
+  </si>
+  <si>
+    <t>-85.395mm</t>
+  </si>
+  <si>
+    <t>U20</t>
+  </si>
+  <si>
+    <t>90.932mm</t>
+  </si>
+  <si>
+    <t>-87.122mm</t>
+  </si>
+  <si>
+    <t>90.307mm</t>
+  </si>
+  <si>
+    <t>-85.522mm</t>
+  </si>
+  <si>
+    <t>U21</t>
+  </si>
+  <si>
+    <t>83.058mm</t>
+  </si>
+  <si>
+    <t>82.433mm</t>
+  </si>
+  <si>
+    <t>U22</t>
+  </si>
+  <si>
+    <t>74.305mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>TLV75733PDBVR</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L2.9-W1.6-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>-45.212mm</t>
+  </si>
+  <si>
+    <t>95.184mm</t>
+  </si>
+  <si>
+    <t>-44.112mm</t>
+  </si>
+  <si>
+    <t>CS1</t>
+  </si>
+  <si>
+    <t>106.045mm</t>
+  </si>
+  <si>
+    <t>CS4</t>
+  </si>
+  <si>
+    <t>CS3</t>
+  </si>
+  <si>
+    <t>83.566mm</t>
+  </si>
+  <si>
+    <t>CS2</t>
+  </si>
+  <si>
+    <t>72.771mm</t>
   </si>
   <si>
     <t>C15</t>
   </si>
   <si>
-    <t>86.487mm</t>
-  </si>
-  <si>
-    <t>-63.5mm</t>
-  </si>
-  <si>
-    <t>-64.045mm</t>
+    <t>CL10A106MO8NQNC</t>
+  </si>
+  <si>
+    <t>93.091mm</t>
+  </si>
+  <si>
+    <t>-40.894mm</t>
+  </si>
+  <si>
+    <t>-40.194mm</t>
+  </si>
+  <si>
+    <t>10uF</t>
   </si>
   <si>
     <t>C16</t>
   </si>
   <si>
-    <t>108.204mm</t>
-  </si>
-  <si>
-    <t>-81.28mm</t>
-  </si>
-  <si>
-    <t>-80.735mm</t>
+    <t>99.06mm</t>
+  </si>
+  <si>
+    <t>-37.846mm</t>
+  </si>
+  <si>
+    <t>-38.546mm</t>
   </si>
   <si>
     <t>C17</t>
   </si>
   <si>
-    <t>-61.087mm</t>
-  </si>
-  <si>
-    <t>-60.542mm</t>
+    <t>06035C104JAT2A</t>
   </si>
   <si>
     <t>C18</t>
   </si>
   <si>
-    <t>88.9mm</t>
-  </si>
-  <si>
-    <t>88.355mm</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>97.626mm</t>
-  </si>
-  <si>
-    <t>-58.711mm</t>
-  </si>
-  <si>
-    <t>98.171mm</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>97.536mm</t>
-  </si>
-  <si>
-    <t>96.991mm</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>97.663mm</t>
-  </si>
-  <si>
-    <t>98.208mm</t>
-  </si>
-  <si>
-    <t>C24</t>
-  </si>
-  <si>
-    <t>-48.768mm</t>
-  </si>
-  <si>
-    <t>C73</t>
-  </si>
-  <si>
-    <t>CC0603JRNPO9BN120</t>
-  </si>
-  <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>78.486mm</t>
-  </si>
-  <si>
-    <t>-43.942mm</t>
-  </si>
-  <si>
-    <t>-44.642mm</t>
-  </si>
-  <si>
-    <t>12pF</t>
-  </si>
-  <si>
-    <t>C74</t>
-  </si>
-  <si>
-    <t>-41.021mm</t>
-  </si>
-  <si>
-    <t>-41.721mm</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>XL2EL89CSI-111YLC-12M</t>
-  </si>
-  <si>
-    <t>CRYSTAL-SMD_4P-L3.2-W2.5-BL</t>
-  </si>
-  <si>
-    <t>75.819mm</t>
-  </si>
-  <si>
-    <t>-42.291mm</t>
-  </si>
-  <si>
-    <t>74.969mm</t>
-  </si>
-  <si>
-    <t>-41.191mm</t>
-  </si>
-  <si>
-    <t>12MHz</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>88.011mm</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>C30</t>
-  </si>
-  <si>
-    <t>96.938mm</t>
-  </si>
-  <si>
-    <t>-81.19mm</t>
-  </si>
-  <si>
-    <t>-80.645mm</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>-65.913mm</t>
-  </si>
-  <si>
-    <t>-66.458mm</t>
-  </si>
-  <si>
-    <t>C32</t>
-  </si>
-  <si>
-    <t>86.614mm</t>
-  </si>
-  <si>
-    <t>87.159mm</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>77.343mm</t>
-  </si>
-  <si>
-    <t>-58.928mm</t>
-  </si>
-  <si>
-    <t>76.798mm</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>77.47mm</t>
-  </si>
-  <si>
-    <t>76.925mm</t>
-  </si>
-  <si>
-    <t>C36</t>
-  </si>
-  <si>
-    <t>-50.038mm</t>
-  </si>
-  <si>
-    <t>85.942mm</t>
-  </si>
-  <si>
-    <t>C37</t>
-  </si>
-  <si>
-    <t>C38</t>
-  </si>
-  <si>
-    <t>77.433mm</t>
-  </si>
-  <si>
-    <t>-48.551mm</t>
-  </si>
-  <si>
-    <t>76.888mm</t>
-  </si>
-  <si>
-    <t>C44</t>
-  </si>
-  <si>
-    <t>85.725mm</t>
-  </si>
-  <si>
-    <t>-80.899mm</t>
-  </si>
-  <si>
-    <t>-80.354mm</t>
-  </si>
-  <si>
-    <t>C46</t>
-  </si>
-  <si>
-    <t>74.549mm</t>
-  </si>
-  <si>
-    <t>75.094mm</t>
-  </si>
-  <si>
-    <t>C47</t>
-  </si>
-  <si>
-    <t>74.575mm</t>
-  </si>
-  <si>
-    <t>-57.759mm</t>
-  </si>
-  <si>
-    <t>75.121mm</t>
-  </si>
-  <si>
-    <t>C48</t>
-  </si>
-  <si>
-    <t>66.003mm</t>
-  </si>
-  <si>
-    <t>65.458mm</t>
-  </si>
-  <si>
-    <t>C49</t>
-  </si>
-  <si>
-    <t>66.002mm</t>
-  </si>
-  <si>
-    <t>-49.62mm</t>
-  </si>
-  <si>
-    <t>65.457mm</t>
-  </si>
-  <si>
-    <t>C50</t>
-  </si>
-  <si>
-    <t>74.676mm</t>
-  </si>
-  <si>
-    <t>-49.784mm</t>
-  </si>
-  <si>
-    <t>74.131mm</t>
-  </si>
-  <si>
-    <t>C51</t>
-  </si>
-  <si>
-    <t>65.405mm</t>
-  </si>
-  <si>
-    <t>-58.42mm</t>
-  </si>
-  <si>
-    <t>-58.965mm</t>
-  </si>
-  <si>
-    <t>C52</t>
-  </si>
-  <si>
-    <t>66.548mm</t>
-  </si>
-  <si>
-    <t>C58</t>
-  </si>
-  <si>
-    <t>74.967mm</t>
-  </si>
-  <si>
-    <t>-80.936mm</t>
-  </si>
-  <si>
-    <t>-80.391mm</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>ESDA6V1L_C587141</t>
-  </si>
-  <si>
-    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
-  </si>
-  <si>
-    <t>103.759mm</t>
-  </si>
-  <si>
-    <t>-81.534mm</t>
-  </si>
-  <si>
-    <t>104.709mm</t>
-  </si>
-  <si>
-    <t>-80.534mm</t>
-  </si>
-  <si>
-    <t>ESDA6V1L</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>92.456mm</t>
-  </si>
-  <si>
-    <t>93.406mm</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>81.28mm</t>
-  </si>
-  <si>
-    <t>82.23mm</t>
-  </si>
-  <si>
-    <t>-80.28mm</t>
+    <t>97.409mm</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>FSMD100-1206R</t>
+  </si>
+  <si>
+    <t>F1206</t>
+  </si>
+  <si>
+    <t>100.838mm</t>
+  </si>
+  <si>
+    <t>-40.005mm</t>
+  </si>
+  <si>
+    <t>-38.56mm</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>NCD0603Y2</t>
+  </si>
+  <si>
+    <t>LED0603-RD</t>
+  </si>
+  <si>
+    <t>105.41mm</t>
+  </si>
+  <si>
+    <t>-47.371mm</t>
+  </si>
+  <si>
+    <t>106.159mm</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>0603WAF2001T5E</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>101.727mm</t>
+  </si>
+  <si>
+    <t>-46.863mm</t>
+  </si>
+  <si>
+    <t>-46.11mm</t>
+  </si>
+  <si>
+    <t>2kΩ</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>TNPW06035K10BEEA</t>
+  </si>
+  <si>
+    <t>102.184mm</t>
+  </si>
+  <si>
+    <t>-36.182mm</t>
+  </si>
+  <si>
+    <t>-35.428mm</t>
+  </si>
+  <si>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>101.676mm</t>
+  </si>
+  <si>
+    <t>-44.038mm</t>
+  </si>
+  <si>
+    <t>-44.792mm</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>SL2.1A</t>
+  </si>
+  <si>
+    <t>SOP-16_L10.0-W3.9-P1.27-LS6.0-BL</t>
+  </si>
+  <si>
+    <t>84.582mm</t>
+  </si>
+  <si>
+    <t>-43.18mm</t>
+  </si>
+  <si>
+    <t>80.137mm</t>
+  </si>
+  <si>
+    <t>-46.052mm</t>
+  </si>
+  <si>
+    <t>USB1</t>
+  </si>
+  <si>
+    <t>TYPEC-304-BCP16_C720629</t>
+  </si>
+  <si>
+    <t>USB-C-SMD_TYPEC-304-BCP16</t>
+  </si>
+  <si>
+    <t>-41.529mm</t>
+  </si>
+  <si>
+    <t>104.285mm</t>
+  </si>
+  <si>
+    <t>-45.849mm</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>TYPEC-304-BCP16</t>
   </si>
   <si>
     <t>D5</t>
   </si>
   <si>
-    <t>70.485mm</t>
-  </si>
-  <si>
-    <t>71.435mm</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>SZYY0603B</t>
-  </si>
-  <si>
-    <t>LED0603-R-RD_BLUE</t>
-  </si>
-  <si>
-    <t>96.774mm</t>
-  </si>
-  <si>
-    <t>-33.02mm</t>
-  </si>
-  <si>
-    <t>-33.871mm</t>
-  </si>
-  <si>
-    <t>LED3</t>
-  </si>
-  <si>
-    <t>SZYY0603G</t>
-  </si>
-  <si>
-    <t>LED0603-R-RD_GREEN</t>
-  </si>
-  <si>
-    <t>98.806mm</t>
-  </si>
-  <si>
-    <t>LED6</t>
-  </si>
-  <si>
-    <t>94.742mm</t>
-  </si>
-  <si>
-    <t>LED7</t>
-  </si>
-  <si>
-    <t>89.916mm</t>
-  </si>
-  <si>
-    <t>LED8</t>
-  </si>
-  <si>
-    <t>91.821mm</t>
-  </si>
-  <si>
-    <t>LED9</t>
-  </si>
-  <si>
-    <t>87.884mm</t>
-  </si>
-  <si>
-    <t>LED10</t>
-  </si>
-  <si>
-    <t>82.69mm</t>
-  </si>
-  <si>
-    <t>-32.994mm</t>
-  </si>
-  <si>
-    <t>-33.845mm</t>
-  </si>
-  <si>
-    <t>LED11</t>
-  </si>
-  <si>
-    <t>84.722mm</t>
-  </si>
-  <si>
-    <t>LED12</t>
-  </si>
-  <si>
-    <t>80.658mm</t>
-  </si>
-  <si>
-    <t>LED13</t>
-  </si>
-  <si>
-    <t>75.324mm</t>
-  </si>
-  <si>
-    <t>-33.007mm</t>
-  </si>
-  <si>
-    <t>-33.858mm</t>
-  </si>
-  <si>
-    <t>LED14</t>
-  </si>
-  <si>
-    <t>LED15</t>
-  </si>
-  <si>
-    <t>73.292mm</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>0402WGF1002TCE</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>108.839mm</t>
-  </si>
-  <si>
-    <t>109.272mm</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>R63</t>
-  </si>
-  <si>
-    <t>105.156mm</t>
-  </si>
-  <si>
-    <t>-59.436mm</t>
-  </si>
-  <si>
-    <t>104.723mm</t>
-  </si>
-  <si>
-    <t>R74</t>
-  </si>
-  <si>
-    <t>0603WAF1200T5E</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>101.473mm</t>
-  </si>
-  <si>
-    <t>-81.661mm</t>
-  </si>
-  <si>
-    <t>-82.414mm</t>
-  </si>
-  <si>
-    <t>120Ω</t>
-  </si>
-  <si>
-    <t>R75</t>
-  </si>
-  <si>
-    <t>0603WAF0000T5E</t>
-  </si>
-  <si>
-    <t>100.584mm</t>
-  </si>
-  <si>
-    <t>-36.195mm</t>
-  </si>
-  <si>
-    <t>-35.442mm</t>
-  </si>
-  <si>
-    <t>0Ω</t>
-  </si>
-  <si>
-    <t>R76</t>
-  </si>
-  <si>
-    <t>0603WAF1001T5E</t>
-  </si>
-  <si>
-    <t>92.583mm</t>
-  </si>
-  <si>
-    <t>-37.973mm</t>
-  </si>
-  <si>
-    <t>-38.726mm</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>R77</t>
-  </si>
-  <si>
-    <t>94.234mm</t>
-  </si>
-  <si>
-    <t>R78</t>
-  </si>
-  <si>
-    <t>95.898mm</t>
-  </si>
-  <si>
-    <t>-37.947mm</t>
-  </si>
-  <si>
-    <t>-38.7mm</t>
-  </si>
-  <si>
-    <t>R79</t>
-  </si>
-  <si>
-    <t>98.096mm</t>
-  </si>
-  <si>
-    <t>R80</t>
-  </si>
-  <si>
-    <t>93.98mm</t>
-  </si>
-  <si>
-    <t>-59.309mm</t>
-  </si>
-  <si>
-    <t>93.547mm</t>
-  </si>
-  <si>
-    <t>R85</t>
-  </si>
-  <si>
-    <t>90.17mm</t>
-  </si>
-  <si>
-    <t>R87</t>
-  </si>
-  <si>
-    <t>87.757mm</t>
-  </si>
-  <si>
-    <t>R88</t>
-  </si>
-  <si>
-    <t>89.408mm</t>
-  </si>
-  <si>
-    <t>R89</t>
-  </si>
-  <si>
-    <t>91.059mm</t>
-  </si>
-  <si>
-    <t>R90</t>
-  </si>
-  <si>
-    <t>-49.022mm</t>
-  </si>
-  <si>
-    <t>87.047mm</t>
-  </si>
-  <si>
-    <t>R91</t>
-  </si>
-  <si>
-    <t>82.677mm</t>
-  </si>
-  <si>
-    <t>82.244mm</t>
-  </si>
-  <si>
-    <t>R96</t>
-  </si>
-  <si>
-    <t>78.994mm</t>
-  </si>
-  <si>
-    <t>-81.788mm</t>
-  </si>
-  <si>
-    <t>-82.541mm</t>
-  </si>
-  <si>
-    <t>R98</t>
-  </si>
-  <si>
-    <t>79.375mm</t>
-  </si>
-  <si>
-    <t>R99</t>
-  </si>
-  <si>
-    <t>81.026mm</t>
-  </si>
-  <si>
-    <t>R100</t>
-  </si>
-  <si>
-    <t>82.423mm</t>
-  </si>
-  <si>
-    <t>R101</t>
-  </si>
-  <si>
-    <t>74.93mm</t>
-  </si>
-  <si>
-    <t>75.363mm</t>
-  </si>
-  <si>
-    <t>R102</t>
-  </si>
-  <si>
-    <t>70.866mm</t>
-  </si>
-  <si>
-    <t>70.433mm</t>
-  </si>
-  <si>
-    <t>R107</t>
-  </si>
-  <si>
-    <t>68.199mm</t>
-  </si>
-  <si>
-    <t>-82.169mm</t>
-  </si>
-  <si>
-    <t>-82.922mm</t>
-  </si>
-  <si>
-    <t>R109</t>
-  </si>
-  <si>
-    <t>74.295mm</t>
-  </si>
-  <si>
-    <t>R110</t>
-  </si>
-  <si>
-    <t>75.946mm</t>
-  </si>
-  <si>
-    <t>R111</t>
-  </si>
-  <si>
-    <t>77.597mm</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>VPT85BB-01A</t>
-  </si>
-  <si>
-    <t>XFMR-SMD_L7.5-W6.7-P2.54-LS7.7-BL</t>
-  </si>
-  <si>
-    <t>75.692mm</t>
-  </si>
-  <si>
-    <t>71.842mm</t>
-  </si>
-  <si>
-    <t>-60.96mm</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>98.933mm</t>
-  </si>
-  <si>
-    <t>102.783mm</t>
-  </si>
-  <si>
-    <t>-66.04mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>STM32G431C8T6</t>
-  </si>
-  <si>
-    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
-  </si>
-  <si>
-    <t>104.394mm</t>
-  </si>
-  <si>
-    <t>-53.594mm</t>
-  </si>
-  <si>
-    <t>108.644mm</t>
-  </si>
-  <si>
-    <t>-56.344mm</t>
-  </si>
-  <si>
-    <t>U20</t>
-  </si>
-  <si>
-    <t>VPS8505</t>
-  </si>
-  <si>
-    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>68.326mm</t>
-  </si>
-  <si>
-    <t>69.676mm</t>
-  </si>
-  <si>
-    <t>-64.45mm</t>
-  </si>
-  <si>
-    <t>U21</t>
-  </si>
-  <si>
-    <t>DSK36_C22466353</t>
-  </si>
-  <si>
-    <t>SOD-123FL_L2.8-W1.9-LS3.7-RD</t>
-  </si>
-  <si>
-    <t>83.312mm</t>
-  </si>
-  <si>
-    <t>85.012mm</t>
-  </si>
-  <si>
-    <t>DSK36</t>
-  </si>
-  <si>
-    <t>U22</t>
-  </si>
-  <si>
-    <t>83.439mm</t>
-  </si>
-  <si>
-    <t>-66.294mm</t>
-  </si>
-  <si>
-    <t>85.139mm</t>
-  </si>
-  <si>
-    <t>U24</t>
-  </si>
-  <si>
-    <t>TPS76350DBVR-TP</t>
-  </si>
-  <si>
-    <t>SOT-23-5_L3.0-W1.6-P0.95-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>82.162mm</t>
-  </si>
-  <si>
-    <t>-62.55mm</t>
-  </si>
-  <si>
-    <t>U25</t>
-  </si>
-  <si>
-    <t>ISO1050DWR</t>
-  </si>
-  <si>
-    <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
-  </si>
-  <si>
-    <t>-73.66mm</t>
-  </si>
-  <si>
-    <t>-68.91mm</t>
-  </si>
-  <si>
-    <t>U26</t>
-  </si>
-  <si>
-    <t>93.218mm</t>
-  </si>
-  <si>
-    <t>97.468mm</t>
-  </si>
-  <si>
-    <t>U29</t>
-  </si>
-  <si>
-    <t>107.061mm</t>
-  </si>
-  <si>
-    <t>105.711mm</t>
-  </si>
-  <si>
-    <t>U30</t>
-  </si>
-  <si>
-    <t>89.359mm</t>
-  </si>
-  <si>
-    <t>U31</t>
-  </si>
-  <si>
-    <t>91.186mm</t>
-  </si>
-  <si>
-    <t>-60.833mm</t>
-  </si>
-  <si>
-    <t>89.486mm</t>
-  </si>
-  <si>
-    <t>U32</t>
-  </si>
-  <si>
-    <t>92.336mm</t>
-  </si>
-  <si>
-    <t>U33</t>
-  </si>
-  <si>
-    <t>96.901mm</t>
-  </si>
-  <si>
-    <t>U34</t>
-  </si>
-  <si>
-    <t>81.915mm</t>
-  </si>
-  <si>
-    <t>-53.721mm</t>
-  </si>
-  <si>
-    <t>86.165mm</t>
-  </si>
-  <si>
-    <t>-56.471mm</t>
-  </si>
-  <si>
-    <t>C75</t>
-  </si>
-  <si>
-    <t>CGA0603X5R226M160JT</t>
-  </si>
-  <si>
-    <t>65.532mm</t>
-  </si>
-  <si>
-    <t>-46.355mm</t>
-  </si>
-  <si>
-    <t>-47.055mm</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>SI2301_C2891731</t>
-  </si>
-  <si>
-    <t>74.168mm</t>
-  </si>
-  <si>
-    <t>-46.228mm</t>
-  </si>
-  <si>
-    <t>73.168mm</t>
-  </si>
-  <si>
-    <t>-45.278mm</t>
-  </si>
-  <si>
-    <t>SI2301</t>
-  </si>
-  <si>
-    <t>U41</t>
-  </si>
-  <si>
-    <t>81.534mm</t>
-  </si>
-  <si>
-    <t>-73.533mm</t>
-  </si>
-  <si>
-    <t>85.979mm</t>
-  </si>
-  <si>
-    <t>-68.783mm</t>
-  </si>
-  <si>
-    <t>U42</t>
-  </si>
-  <si>
-    <t>70.231mm</t>
-  </si>
-  <si>
-    <t>74.481mm</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>SS8050_C916392</t>
-  </si>
-  <si>
-    <t>69.596mm</t>
-  </si>
-  <si>
-    <t>68.596mm</t>
-  </si>
-  <si>
-    <t>-45.405mm</t>
-  </si>
-  <si>
-    <t>SS8050</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>0603WAF1004T5E</t>
-  </si>
-  <si>
-    <t>67.183mm</t>
-  </si>
-  <si>
-    <t>-45.602mm</t>
-  </si>
-  <si>
-    <t>1MΩ</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>RCA03100KJLF</t>
-  </si>
-  <si>
-    <t>72.009mm</t>
-  </si>
-  <si>
-    <t>-45.475mm</t>
-  </si>
-  <si>
-    <t>100kΩ</t>
-  </si>
-  <si>
-    <t>TP1</t>
-  </si>
-  <si>
-    <t>Test-Point</t>
-  </si>
-  <si>
-    <t>Test-Point-0.5mm</t>
-  </si>
-  <si>
-    <t>69.5mm</t>
-  </si>
-  <si>
-    <t>-56.238mm</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>TP2</t>
-  </si>
-  <si>
-    <t>70.75mm</t>
-  </si>
-  <si>
-    <t>TP3</t>
-  </si>
-  <si>
-    <t>67mm</t>
-  </si>
-  <si>
-    <t>U49</t>
-  </si>
-  <si>
-    <t>TP4</t>
-  </si>
-  <si>
-    <t>68.25mm</t>
-  </si>
-  <si>
-    <t>TP5</t>
-  </si>
-  <si>
-    <t>92.5mm</t>
-  </si>
-  <si>
-    <t>-55.785mm</t>
-  </si>
-  <si>
-    <t>TP6</t>
-  </si>
-  <si>
-    <t>93.75mm</t>
-  </si>
-  <si>
-    <t>TP7</t>
-  </si>
-  <si>
-    <t>90mm</t>
-  </si>
-  <si>
-    <t>TP8</t>
-  </si>
-  <si>
-    <t>91.25mm</t>
-  </si>
-  <si>
-    <t>TP9</t>
-  </si>
-  <si>
-    <t>103.5mm</t>
-  </si>
-  <si>
-    <t>-56.023mm</t>
-  </si>
-  <si>
-    <t>TP10</t>
-  </si>
-  <si>
-    <t>104.75mm</t>
-  </si>
-  <si>
-    <t>TP11</t>
-  </si>
-  <si>
-    <t>101mm</t>
-  </si>
-  <si>
-    <t>C71</t>
-  </si>
-  <si>
-    <t>CL10A106MO8NQNC</t>
-  </si>
-  <si>
-    <t>84.201mm</t>
-  </si>
-  <si>
-    <t>-38.673mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C72</t>
-  </si>
-  <si>
-    <t>TP12</t>
-  </si>
-  <si>
-    <t>102.25mm</t>
-  </si>
-  <si>
-    <t>TP13</t>
-  </si>
-  <si>
-    <t>81mm</t>
-  </si>
-  <si>
-    <t>-56.397mm</t>
-  </si>
-  <si>
-    <t>TP14</t>
-  </si>
-  <si>
-    <t>82.25mm</t>
-  </si>
-  <si>
-    <t>TP15</t>
-  </si>
-  <si>
-    <t>78.5mm</t>
-  </si>
-  <si>
-    <t>TP16</t>
-  </si>
-  <si>
-    <t>79.75mm</t>
-  </si>
-  <si>
-    <t>C76</t>
-  </si>
-  <si>
-    <t>108.56mm</t>
-  </si>
-  <si>
-    <t>-65.636mm</t>
-  </si>
-  <si>
-    <t>108.015mm</t>
-  </si>
-  <si>
-    <t>C77</t>
-  </si>
-  <si>
-    <t>105.918mm</t>
-  </si>
-  <si>
-    <t>-65.659mm</t>
-  </si>
-  <si>
-    <t>105.373mm</t>
-  </si>
-  <si>
-    <t>C78</t>
-  </si>
-  <si>
-    <t>68.961mm</t>
-  </si>
-  <si>
-    <t>-65.786mm</t>
-  </si>
-  <si>
-    <t>69.506mm</t>
-  </si>
-  <si>
-    <t>C79</t>
-  </si>
-  <si>
-    <t>66.294mm</t>
-  </si>
-  <si>
-    <t>65.749mm</t>
-  </si>
-  <si>
-    <t>U52</t>
-  </si>
-  <si>
-    <t>SM02B-GHS-TB(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-SMD_SM02B-GHS-TB-LF-SN</t>
-  </si>
-  <si>
-    <t>-86.995mm</t>
-  </si>
-  <si>
-    <t>98.181mm</t>
-  </si>
-  <si>
-    <t>-85.395mm</t>
-  </si>
-  <si>
-    <t>U53</t>
-  </si>
-  <si>
-    <t>90.932mm</t>
-  </si>
-  <si>
-    <t>-87.122mm</t>
-  </si>
-  <si>
-    <t>90.307mm</t>
-  </si>
-  <si>
-    <t>-85.522mm</t>
-  </si>
-  <si>
-    <t>U54</t>
-  </si>
-  <si>
-    <t>83.058mm</t>
-  </si>
-  <si>
-    <t>82.433mm</t>
-  </si>
-  <si>
-    <t>U55</t>
-  </si>
-  <si>
-    <t>74.305mm</t>
-  </si>
-  <si>
-    <t>U56</t>
-  </si>
-  <si>
-    <t>TLV75733PDBVR</t>
-  </si>
-  <si>
-    <t>SOT-23-5_L2.9-W1.6-P0.95-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>-45.212mm</t>
-  </si>
-  <si>
-    <t>95.184mm</t>
-  </si>
-  <si>
-    <t>-44.112mm</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
     <t>SMBJ6.0CA_C113977</t>
   </si>
   <si>
@@ -1465,196 +1642,10 @@
     <t>-43.688mm</t>
   </si>
   <si>
-    <t>-46.279mm</t>
+    <t>-46.079mm</t>
   </si>
   <si>
     <t>SMBJ6.0CA</t>
-  </si>
-  <si>
-    <t>CS1</t>
-  </si>
-  <si>
-    <t>106.045mm</t>
-  </si>
-  <si>
-    <t>CS2</t>
-  </si>
-  <si>
-    <t>CS3</t>
-  </si>
-  <si>
-    <t>83.566mm</t>
-  </si>
-  <si>
-    <t>CS4</t>
-  </si>
-  <si>
-    <t>72.771mm</t>
-  </si>
-  <si>
-    <t>C61</t>
-  </si>
-  <si>
-    <t>93.091mm</t>
-  </si>
-  <si>
-    <t>-40.894mm</t>
-  </si>
-  <si>
-    <t>-40.194mm</t>
-  </si>
-  <si>
-    <t>C62</t>
-  </si>
-  <si>
-    <t>99.06mm</t>
-  </si>
-  <si>
-    <t>-37.846mm</t>
-  </si>
-  <si>
-    <t>-38.546mm</t>
-  </si>
-  <si>
-    <t>C63</t>
-  </si>
-  <si>
-    <t>06035C104JAT2A</t>
-  </si>
-  <si>
-    <t>C64</t>
-  </si>
-  <si>
-    <t>97.409mm</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>FSMD100-1206R</t>
-  </si>
-  <si>
-    <t>F1206</t>
-  </si>
-  <si>
-    <t>100.838mm</t>
-  </si>
-  <si>
-    <t>-40.005mm</t>
-  </si>
-  <si>
-    <t>-38.56mm</t>
-  </si>
-  <si>
-    <t>LED16</t>
-  </si>
-  <si>
-    <t>NCD0603Y2</t>
-  </si>
-  <si>
-    <t>LED0603-RD</t>
-  </si>
-  <si>
-    <t>105.41mm</t>
-  </si>
-  <si>
-    <t>-47.371mm</t>
-  </si>
-  <si>
-    <t>106.159mm</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>0603WAF2001T5E</t>
-  </si>
-  <si>
-    <t>101.727mm</t>
-  </si>
-  <si>
-    <t>-46.863mm</t>
-  </si>
-  <si>
-    <t>-46.11mm</t>
-  </si>
-  <si>
-    <t>2kΩ</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>TNPW06035K10BEEA</t>
-  </si>
-  <si>
-    <t>102.184mm</t>
-  </si>
-  <si>
-    <t>-36.182mm</t>
-  </si>
-  <si>
-    <t>-36.935mm</t>
-  </si>
-  <si>
-    <t>5.1kΩ</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>101.676mm</t>
-  </si>
-  <si>
-    <t>-44.038mm</t>
-  </si>
-  <si>
-    <t>-44.792mm</t>
-  </si>
-  <si>
-    <t>U50</t>
-  </si>
-  <si>
-    <t>SL2.1A</t>
-  </si>
-  <si>
-    <t>SOP-16_L10.0-W3.9-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>84.582mm</t>
-  </si>
-  <si>
-    <t>-43.18mm</t>
-  </si>
-  <si>
-    <t>80.137mm</t>
-  </si>
-  <si>
-    <t>-46.052mm</t>
-  </si>
-  <si>
-    <t>USB9</t>
-  </si>
-  <si>
-    <t>TYPEC-304-BCP16_C720629</t>
-  </si>
-  <si>
-    <t>USB-C-SMD_TYPEC-304-BCP16</t>
-  </si>
-  <si>
-    <t>-41.529mm</t>
-  </si>
-  <si>
-    <t>104.285mm</t>
-  </si>
-  <si>
-    <t>-45.849mm</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>TYPEC-304-BCP16</t>
   </si>
 </sst>
 </file>
@@ -2031,7 +2022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O151"/>
+  <dimension ref="A1:O149"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -3059,7 +3050,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M22" t="s">
         <v>22</v>
@@ -7635,98 +7626,98 @@
         <v>425</v>
       </c>
       <c r="B120" t="s">
+        <v>397</v>
+      </c>
+      <c r="C120" t="s">
+        <v>398</v>
+      </c>
+      <c r="D120" t="s">
         <v>426</v>
       </c>
-      <c r="C120" t="s">
-        <v>86</v>
-      </c>
-      <c r="D120" t="s">
-        <v>427</v>
-      </c>
       <c r="E120" t="s">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="F120" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G120" t="s">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="H120" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I120" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="J120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K120" t="s">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="L120">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M120" t="s">
         <v>22</v>
       </c>
       <c r="N120" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="O120" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B121" t="s">
-        <v>426</v>
+        <v>397</v>
       </c>
       <c r="C121" t="s">
-        <v>86</v>
+        <v>398</v>
       </c>
       <c r="D121" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="E121" t="s">
-        <v>240</v>
+        <v>429</v>
       </c>
       <c r="F121" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="G121" t="s">
-        <v>240</v>
+        <v>429</v>
       </c>
       <c r="H121" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="I121" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="L121">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M121" t="s">
         <v>22</v>
       </c>
       <c r="N121" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="O121" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B122" t="s">
         <v>397</v>
@@ -7735,22 +7726,22 @@
         <v>398</v>
       </c>
       <c r="D122" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E122" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F122" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G122" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="H122" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I122" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="J122">
         <v>1</v>
@@ -7773,7 +7764,7 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B123" t="s">
         <v>397</v>
@@ -7782,22 +7773,22 @@
         <v>398</v>
       </c>
       <c r="D123" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E123" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="F123" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G123" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="H123" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I123" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="J123">
         <v>1</v>
@@ -7820,7 +7811,7 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B124" t="s">
         <v>397</v>
@@ -7829,22 +7820,22 @@
         <v>398</v>
       </c>
       <c r="D124" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E124" t="s">
+        <v>429</v>
+      </c>
+      <c r="F124" t="s">
         <v>435</v>
       </c>
-      <c r="F124" t="s">
-        <v>437</v>
-      </c>
       <c r="G124" t="s">
+        <v>429</v>
+      </c>
+      <c r="H124" t="s">
         <v>435</v>
       </c>
-      <c r="H124" t="s">
-        <v>437</v>
-      </c>
       <c r="I124" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="J124">
         <v>1</v>
@@ -7867,49 +7858,49 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>436</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>437</v>
+      </c>
+      <c r="E125" t="s">
         <v>438</v>
       </c>
-      <c r="B125" t="s">
-        <v>397</v>
-      </c>
-      <c r="C125" t="s">
-        <v>398</v>
-      </c>
-      <c r="D125" t="s">
-        <v>439</v>
-      </c>
-      <c r="E125" t="s">
-        <v>435</v>
-      </c>
       <c r="F125" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G125" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="H125" t="s">
         <v>439</v>
       </c>
       <c r="I125" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="L125">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M125" t="s">
         <v>22</v>
       </c>
       <c r="N125" t="s">
-        <v>397</v>
+        <v>23</v>
       </c>
       <c r="O125" t="s">
-        <v>397</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
@@ -7917,51 +7908,51 @@
         <v>440</v>
       </c>
       <c r="B126" t="s">
-        <v>397</v>
+        <v>16</v>
       </c>
       <c r="C126" t="s">
-        <v>398</v>
+        <v>17</v>
       </c>
       <c r="D126" t="s">
         <v>441</v>
       </c>
       <c r="E126" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="F126" t="s">
         <v>441</v>
       </c>
       <c r="G126" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="H126" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I126" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="J126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="L126">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M126" t="s">
         <v>22</v>
       </c>
       <c r="N126" t="s">
-        <v>397</v>
+        <v>23</v>
       </c>
       <c r="O126" t="s">
-        <v>397</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B127" t="s">
         <v>16</v>
@@ -7970,22 +7961,22 @@
         <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E127" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F127" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G127" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H127" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I127" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J127">
         <v>2</v>
@@ -7994,7 +7985,7 @@
         <v>21</v>
       </c>
       <c r="L127">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M127" t="s">
         <v>22</v>
@@ -8008,7 +7999,7 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B128" t="s">
         <v>16</v>
@@ -8017,22 +8008,22 @@
         <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E128" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F128" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G128" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H128" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I128" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J128">
         <v>2</v>
@@ -8055,81 +8046,81 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B129" t="s">
-        <v>16</v>
+        <v>452</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>453</v>
       </c>
       <c r="D129" t="s">
-        <v>451</v>
+        <v>190</v>
       </c>
       <c r="E129" t="s">
+        <v>454</v>
+      </c>
+      <c r="F129" t="s">
+        <v>190</v>
+      </c>
+      <c r="G129" t="s">
+        <v>454</v>
+      </c>
+      <c r="H129" t="s">
+        <v>455</v>
+      </c>
+      <c r="I129" t="s">
+        <v>456</v>
+      </c>
+      <c r="J129">
+        <v>4</v>
+      </c>
+      <c r="K129" t="s">
+        <v>21</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129" t="s">
+        <v>22</v>
+      </c>
+      <c r="N129" t="s">
         <v>452</v>
       </c>
-      <c r="F129" t="s">
-        <v>451</v>
-      </c>
-      <c r="G129" t="s">
+      <c r="O129" t="s">
         <v>452</v>
-      </c>
-      <c r="H129" t="s">
-        <v>453</v>
-      </c>
-      <c r="I129" t="s">
-        <v>452</v>
-      </c>
-      <c r="J129">
-        <v>2</v>
-      </c>
-      <c r="K129" t="s">
-        <v>21</v>
-      </c>
-      <c r="L129">
-        <v>180</v>
-      </c>
-      <c r="M129" t="s">
-        <v>22</v>
-      </c>
-      <c r="N129" t="s">
-        <v>23</v>
-      </c>
-      <c r="O129" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>452</v>
       </c>
       <c r="C130" t="s">
-        <v>17</v>
+        <v>453</v>
       </c>
       <c r="D130" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E130" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="F130" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G130" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="H130" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="I130" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="J130">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K130" t="s">
         <v>21</v>
@@ -8141,39 +8132,39 @@
         <v>22</v>
       </c>
       <c r="N130" t="s">
-        <v>23</v>
+        <v>452</v>
       </c>
       <c r="O130" t="s">
-        <v>23</v>
+        <v>452</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B131" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C131" t="s">
+        <v>453</v>
+      </c>
+      <c r="D131" t="s">
+        <v>463</v>
+      </c>
+      <c r="E131" t="s">
         <v>459</v>
       </c>
-      <c r="D131" t="s">
-        <v>190</v>
-      </c>
-      <c r="E131" t="s">
-        <v>460</v>
-      </c>
       <c r="F131" t="s">
-        <v>190</v>
+        <v>463</v>
       </c>
       <c r="G131" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H131" t="s">
+        <v>464</v>
+      </c>
+      <c r="I131" t="s">
         <v>461</v>
-      </c>
-      <c r="I131" t="s">
-        <v>462</v>
       </c>
       <c r="J131">
         <v>4</v>
@@ -8188,39 +8179,39 @@
         <v>22</v>
       </c>
       <c r="N131" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="O131" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B132" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C132" t="s">
+        <v>453</v>
+      </c>
+      <c r="D132" t="s">
+        <v>280</v>
+      </c>
+      <c r="E132" t="s">
         <v>459</v>
       </c>
-      <c r="D132" t="s">
-        <v>464</v>
-      </c>
-      <c r="E132" t="s">
-        <v>465</v>
-      </c>
       <c r="F132" t="s">
-        <v>464</v>
+        <v>280</v>
       </c>
       <c r="G132" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="H132" t="s">
         <v>466</v>
       </c>
       <c r="I132" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="J132">
         <v>4</v>
@@ -8235,180 +8226,180 @@
         <v>22</v>
       </c>
       <c r="N132" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="O132" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>467</v>
+      </c>
+      <c r="B133" t="s">
         <v>468</v>
       </c>
-      <c r="B133" t="s">
-        <v>458</v>
-      </c>
       <c r="C133" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="D133" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
       <c r="E133" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="F133" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
       <c r="G133" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="H133" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I133" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="J133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K133" t="s">
         <v>21</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M133" t="s">
         <v>22</v>
       </c>
       <c r="N133" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="O133" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B134" t="s">
-        <v>458</v>
+        <v>232</v>
       </c>
       <c r="C134" t="s">
-        <v>459</v>
+        <v>226</v>
       </c>
       <c r="D134" t="s">
-        <v>280</v>
+        <v>474</v>
       </c>
       <c r="E134" t="s">
-        <v>465</v>
+        <v>271</v>
       </c>
       <c r="F134" t="s">
-        <v>280</v>
+        <v>474</v>
       </c>
       <c r="G134" t="s">
-        <v>465</v>
+        <v>271</v>
       </c>
       <c r="H134" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I134" t="s">
-        <v>467</v>
+        <v>272</v>
       </c>
       <c r="J134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K134" t="s">
         <v>21</v>
       </c>
       <c r="L134">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M134" t="s">
         <v>22</v>
       </c>
       <c r="N134" t="s">
-        <v>458</v>
+        <v>236</v>
       </c>
       <c r="O134" t="s">
-        <v>458</v>
+        <v>236</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B135" t="s">
-        <v>474</v>
+        <v>232</v>
       </c>
       <c r="C135" t="s">
-        <v>475</v>
+        <v>226</v>
       </c>
       <c r="D135" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="E135" t="s">
-        <v>476</v>
+        <v>228</v>
       </c>
       <c r="F135" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="G135" t="s">
-        <v>476</v>
+        <v>228</v>
       </c>
       <c r="H135" t="s">
-        <v>477</v>
+        <v>192</v>
       </c>
       <c r="I135" t="s">
-        <v>478</v>
+        <v>229</v>
       </c>
       <c r="J135">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K135" t="s">
         <v>21</v>
       </c>
       <c r="L135">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M135" t="s">
         <v>22</v>
       </c>
       <c r="N135" t="s">
-        <v>474</v>
+        <v>236</v>
       </c>
       <c r="O135" t="s">
-        <v>474</v>
+        <v>236</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B136" t="s">
-        <v>480</v>
+        <v>232</v>
       </c>
       <c r="C136" t="s">
-        <v>481</v>
+        <v>226</v>
       </c>
       <c r="D136" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E136" t="s">
-        <v>483</v>
+        <v>271</v>
       </c>
       <c r="F136" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G136" t="s">
-        <v>483</v>
+        <v>271</v>
       </c>
       <c r="H136" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I136" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="J136">
         <v>2</v>
@@ -8423,15 +8414,15 @@
         <v>22</v>
       </c>
       <c r="N136" t="s">
-        <v>485</v>
+        <v>236</v>
       </c>
       <c r="O136" t="s">
-        <v>485</v>
+        <v>236</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="B137" t="s">
         <v>232</v>
@@ -8440,22 +8431,22 @@
         <v>226</v>
       </c>
       <c r="D137" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="E137" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="F137" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="G137" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="H137" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="I137" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="J137">
         <v>2</v>
@@ -8478,31 +8469,31 @@
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B138" t="s">
-        <v>232</v>
+        <v>481</v>
       </c>
       <c r="C138" t="s">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="D138" t="s">
-        <v>192</v>
+        <v>482</v>
       </c>
       <c r="E138" t="s">
-        <v>228</v>
+        <v>483</v>
       </c>
       <c r="F138" t="s">
-        <v>192</v>
+        <v>482</v>
       </c>
       <c r="G138" t="s">
-        <v>228</v>
+        <v>483</v>
       </c>
       <c r="H138" t="s">
-        <v>192</v>
+        <v>482</v>
       </c>
       <c r="I138" t="s">
-        <v>229</v>
+        <v>484</v>
       </c>
       <c r="J138">
         <v>2</v>
@@ -8511,45 +8502,45 @@
         <v>21</v>
       </c>
       <c r="L138">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M138" t="s">
         <v>22</v>
       </c>
       <c r="N138" t="s">
-        <v>236</v>
+        <v>485</v>
       </c>
       <c r="O138" t="s">
-        <v>236</v>
+        <v>485</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>486</v>
+      </c>
+      <c r="B139" t="s">
+        <v>481</v>
+      </c>
+      <c r="C139" t="s">
+        <v>86</v>
+      </c>
+      <c r="D139" t="s">
+        <v>487</v>
+      </c>
+      <c r="E139" t="s">
+        <v>488</v>
+      </c>
+      <c r="F139" t="s">
+        <v>487</v>
+      </c>
+      <c r="G139" t="s">
+        <v>488</v>
+      </c>
+      <c r="H139" t="s">
+        <v>487</v>
+      </c>
+      <c r="I139" t="s">
         <v>489</v>
-      </c>
-      <c r="B139" t="s">
-        <v>232</v>
-      </c>
-      <c r="C139" t="s">
-        <v>226</v>
-      </c>
-      <c r="D139" t="s">
-        <v>490</v>
-      </c>
-      <c r="E139" t="s">
-        <v>271</v>
-      </c>
-      <c r="F139" t="s">
-        <v>490</v>
-      </c>
-      <c r="G139" t="s">
-        <v>271</v>
-      </c>
-      <c r="H139" t="s">
-        <v>490</v>
-      </c>
-      <c r="I139" t="s">
-        <v>272</v>
       </c>
       <c r="J139">
         <v>2</v>
@@ -8564,39 +8555,39 @@
         <v>22</v>
       </c>
       <c r="N139" t="s">
-        <v>236</v>
+        <v>485</v>
       </c>
       <c r="O139" t="s">
-        <v>236</v>
+        <v>485</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>490</v>
+      </c>
+      <c r="B140" t="s">
         <v>491</v>
       </c>
-      <c r="B140" t="s">
-        <v>232</v>
-      </c>
       <c r="C140" t="s">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="D140" t="s">
-        <v>492</v>
+        <v>192</v>
       </c>
       <c r="E140" t="s">
-        <v>287</v>
+        <v>483</v>
       </c>
       <c r="F140" t="s">
-        <v>492</v>
+        <v>192</v>
       </c>
       <c r="G140" t="s">
-        <v>287</v>
+        <v>483</v>
       </c>
       <c r="H140" t="s">
-        <v>492</v>
+        <v>192</v>
       </c>
       <c r="I140" t="s">
-        <v>288</v>
+        <v>484</v>
       </c>
       <c r="J140">
         <v>2</v>
@@ -8605,45 +8596,45 @@
         <v>21</v>
       </c>
       <c r="L140">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M140" t="s">
         <v>22</v>
       </c>
       <c r="N140" t="s">
-        <v>236</v>
+        <v>23</v>
       </c>
       <c r="O140" t="s">
-        <v>236</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B141" t="s">
-        <v>426</v>
+        <v>491</v>
       </c>
       <c r="C141" t="s">
         <v>86</v>
       </c>
       <c r="D141" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E141" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F141" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G141" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="H141" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I141" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="J141">
         <v>2</v>
@@ -8652,46 +8643,46 @@
         <v>21</v>
       </c>
       <c r="L141">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M141" t="s">
         <v>22</v>
       </c>
       <c r="N141" t="s">
-        <v>429</v>
+        <v>23</v>
       </c>
       <c r="O141" t="s">
-        <v>429</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>494</v>
+      </c>
+      <c r="B142" t="s">
+        <v>495</v>
+      </c>
+      <c r="C142" t="s">
+        <v>496</v>
+      </c>
+      <c r="D142" t="s">
         <v>497</v>
       </c>
-      <c r="B142" t="s">
-        <v>426</v>
-      </c>
-      <c r="C142" t="s">
-        <v>86</v>
-      </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>498</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
+        <v>497</v>
+      </c>
+      <c r="G142" t="s">
+        <v>498</v>
+      </c>
+      <c r="H142" t="s">
+        <v>497</v>
+      </c>
+      <c r="I142" t="s">
         <v>499</v>
       </c>
-      <c r="F142" t="s">
-        <v>498</v>
-      </c>
-      <c r="G142" t="s">
-        <v>499</v>
-      </c>
-      <c r="H142" t="s">
-        <v>498</v>
-      </c>
-      <c r="I142" t="s">
-        <v>500</v>
-      </c>
       <c r="J142">
         <v>2</v>
       </c>
@@ -8699,45 +8690,45 @@
         <v>21</v>
       </c>
       <c r="L142">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M142" t="s">
         <v>22</v>
       </c>
       <c r="N142" t="s">
-        <v>429</v>
+        <v>495</v>
       </c>
       <c r="O142" t="s">
-        <v>429</v>
+        <v>495</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>500</v>
+      </c>
+      <c r="B143" t="s">
         <v>501</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>502</v>
       </c>
-      <c r="C143" t="s">
-        <v>86</v>
-      </c>
       <c r="D143" t="s">
-        <v>192</v>
+        <v>503</v>
       </c>
       <c r="E143" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="F143" t="s">
-        <v>192</v>
+        <v>503</v>
       </c>
       <c r="G143" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="H143" t="s">
-        <v>192</v>
+        <v>505</v>
       </c>
       <c r="I143" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="J143">
         <v>2</v>
@@ -8746,45 +8737,45 @@
         <v>21</v>
       </c>
       <c r="L143">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M143" t="s">
         <v>22</v>
       </c>
       <c r="N143" t="s">
-        <v>23</v>
+        <v>501</v>
       </c>
       <c r="O143" t="s">
-        <v>23</v>
+        <v>501</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B144" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C144" t="s">
-        <v>86</v>
+        <v>508</v>
       </c>
       <c r="D144" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E144" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F144" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="G144" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="H144" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="I144" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="J144">
         <v>2</v>
@@ -8793,45 +8784,45 @@
         <v>21</v>
       </c>
       <c r="L144">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M144" t="s">
         <v>22</v>
       </c>
       <c r="N144" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
       <c r="O144" t="s">
-        <v>23</v>
+        <v>512</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B145" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C145" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D145" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="E145" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="F145" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="G145" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="H145" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="I145" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="J145">
         <v>2</v>
@@ -8846,39 +8837,39 @@
         <v>22</v>
       </c>
       <c r="N145" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="O145" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B146" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C146" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="D146" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E146" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="F146" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="G146" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="H146" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="I146" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="J146">
         <v>2</v>
@@ -8887,95 +8878,95 @@
         <v>21</v>
       </c>
       <c r="L146">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M146" t="s">
         <v>22</v>
       </c>
       <c r="N146" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="O146" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B147" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C147" t="s">
-        <v>226</v>
+        <v>525</v>
       </c>
       <c r="D147" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="E147" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="F147" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G147" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="H147" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="I147" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J147">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K147" t="s">
         <v>21</v>
       </c>
       <c r="L147">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M147" t="s">
         <v>22</v>
       </c>
       <c r="N147" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O147" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="B148" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C148" t="s">
-        <v>226</v>
+        <v>532</v>
       </c>
       <c r="D148" t="s">
-        <v>525</v>
+        <v>441</v>
       </c>
       <c r="E148" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F148" t="s">
-        <v>525</v>
+        <v>441</v>
       </c>
       <c r="G148" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="H148" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="I148" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="J148">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K148" t="s">
         <v>21</v>
@@ -8984,42 +8975,42 @@
         <v>90</v>
       </c>
       <c r="M148" t="s">
-        <v>22</v>
+        <v>536</v>
       </c>
       <c r="N148" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="O148" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="B149" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="C149" t="s">
-        <v>226</v>
+        <v>540</v>
       </c>
       <c r="D149" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="E149" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="F149" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="G149" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="H149" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="I149" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="J149">
         <v>2</v>
@@ -9034,104 +9025,10 @@
         <v>22</v>
       </c>
       <c r="N149" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="O149" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>533</v>
-      </c>
-      <c r="B150" t="s">
-        <v>534</v>
-      </c>
-      <c r="C150" t="s">
-        <v>535</v>
-      </c>
-      <c r="D150" t="s">
-        <v>536</v>
-      </c>
-      <c r="E150" t="s">
-        <v>537</v>
-      </c>
-      <c r="F150" t="s">
-        <v>536</v>
-      </c>
-      <c r="G150" t="s">
-        <v>537</v>
-      </c>
-      <c r="H150" t="s">
-        <v>538</v>
-      </c>
-      <c r="I150" t="s">
-        <v>539</v>
-      </c>
-      <c r="J150">
-        <v>16</v>
-      </c>
-      <c r="K150" t="s">
-        <v>21</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150" t="s">
-        <v>22</v>
-      </c>
-      <c r="N150" t="s">
-        <v>534</v>
-      </c>
-      <c r="O150" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>540</v>
-      </c>
-      <c r="B151" t="s">
-        <v>541</v>
-      </c>
-      <c r="C151" t="s">
-        <v>542</v>
-      </c>
-      <c r="D151" t="s">
-        <v>447</v>
-      </c>
-      <c r="E151" t="s">
-        <v>543</v>
-      </c>
-      <c r="F151" t="s">
-        <v>447</v>
-      </c>
-      <c r="G151" t="s">
-        <v>543</v>
-      </c>
-      <c r="H151" t="s">
         <v>544</v>
-      </c>
-      <c r="I151" t="s">
-        <v>545</v>
-      </c>
-      <c r="J151">
-        <v>16</v>
-      </c>
-      <c r="K151" t="s">
-        <v>21</v>
-      </c>
-      <c r="L151">
-        <v>90</v>
-      </c>
-      <c r="M151" t="s">
-        <v>546</v>
-      </c>
-      <c r="N151" t="s">
-        <v>547</v>
-      </c>
-      <c r="O151" t="s">
-        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/atom01_pcb/Roboto_Usb2Can/02_Assembly/PickAndPlace_HUB_USBTOCAN_V1_0.xlsx
+++ b/atom01_pcb/Roboto_Usb2Can/02_Assembly/PickAndPlace_HUB_USBTOCAN_V1_0.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_Roboto_uUsb2Can_V1" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_HUB_USBTOCAN_V1_0" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="548">
   <si>
     <t>Designator</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>C39</t>
+    <t>C2</t>
   </si>
   <si>
     <t>CL05B104KB54PNC</t>
@@ -85,396 +85,396 @@
     <t>100nF</t>
   </si>
   <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>100.076mm</t>
+  </si>
+  <si>
+    <t>-57.658mm</t>
+  </si>
+  <si>
+    <t>99.531mm</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>100.05mm</t>
+  </si>
+  <si>
+    <t>-58.775mm</t>
+  </si>
+  <si>
+    <t>99.505mm</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>108.712mm</t>
+  </si>
+  <si>
+    <t>-58.801mm</t>
+  </si>
+  <si>
+    <t>109.257mm</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>-48.514mm</t>
+  </si>
+  <si>
+    <t>108.167mm</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>100.293mm</t>
+  </si>
+  <si>
+    <t>-46.826mm</t>
+  </si>
+  <si>
+    <t>-46.281mm</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>-57.785mm</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>CL05A105KA5NQNC</t>
+  </si>
+  <si>
+    <t>68.834mm</t>
+  </si>
+  <si>
+    <t>-61.341mm</t>
+  </si>
+  <si>
+    <t>69.379mm</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>86.524mm</t>
+  </si>
+  <si>
+    <t>-65.871mm</t>
+  </si>
+  <si>
+    <t>-66.416mm</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>86.487mm</t>
+  </si>
+  <si>
+    <t>-63.5mm</t>
+  </si>
+  <si>
+    <t>-64.045mm</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>108.204mm</t>
+  </si>
+  <si>
+    <t>-81.28mm</t>
+  </si>
+  <si>
+    <t>-80.735mm</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>-61.087mm</t>
+  </si>
+  <si>
+    <t>-60.542mm</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>88.9mm</t>
+  </si>
+  <si>
+    <t>88.355mm</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>97.626mm</t>
+  </si>
+  <si>
+    <t>-58.711mm</t>
+  </si>
+  <si>
+    <t>98.171mm</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>97.536mm</t>
+  </si>
+  <si>
+    <t>96.991mm</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>97.663mm</t>
+  </si>
+  <si>
+    <t>98.208mm</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>-48.768mm</t>
+  </si>
+  <si>
+    <t>C73</t>
+  </si>
+  <si>
+    <t>CC0603JRNPO9BN120</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>78.486mm</t>
+  </si>
+  <si>
+    <t>-43.942mm</t>
+  </si>
+  <si>
+    <t>-44.642mm</t>
+  </si>
+  <si>
+    <t>12pF</t>
+  </si>
+  <si>
+    <t>C74</t>
+  </si>
+  <si>
+    <t>-41.021mm</t>
+  </si>
+  <si>
+    <t>-41.721mm</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>XL2EL89CSI-111YLC-12M</t>
+  </si>
+  <si>
+    <t>CRYSTAL-SMD_4P-L3.2-W2.5-BL</t>
+  </si>
+  <si>
+    <t>75.819mm</t>
+  </si>
+  <si>
+    <t>-42.291mm</t>
+  </si>
+  <si>
+    <t>74.969mm</t>
+  </si>
+  <si>
+    <t>-41.191mm</t>
+  </si>
+  <si>
+    <t>12MHz</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>88.011mm</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>96.938mm</t>
+  </si>
+  <si>
+    <t>-81.19mm</t>
+  </si>
+  <si>
+    <t>-80.645mm</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>-65.913mm</t>
+  </si>
+  <si>
+    <t>-66.458mm</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>86.614mm</t>
+  </si>
+  <si>
+    <t>87.159mm</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>77.343mm</t>
+  </si>
+  <si>
+    <t>-58.928mm</t>
+  </si>
+  <si>
+    <t>76.798mm</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>77.47mm</t>
+  </si>
+  <si>
+    <t>76.925mm</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>-50.038mm</t>
+  </si>
+  <si>
+    <t>85.942mm</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>77.433mm</t>
+  </si>
+  <si>
+    <t>-48.551mm</t>
+  </si>
+  <si>
+    <t>76.888mm</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>85.725mm</t>
+  </si>
+  <si>
+    <t>-80.899mm</t>
+  </si>
+  <si>
+    <t>-80.354mm</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>74.549mm</t>
+  </si>
+  <si>
+    <t>75.094mm</t>
+  </si>
+  <si>
+    <t>C47</t>
+  </si>
+  <si>
+    <t>74.575mm</t>
+  </si>
+  <si>
+    <t>-57.759mm</t>
+  </si>
+  <si>
+    <t>75.121mm</t>
+  </si>
+  <si>
+    <t>C48</t>
+  </si>
+  <si>
+    <t>66.003mm</t>
+  </si>
+  <si>
+    <t>65.458mm</t>
+  </si>
+  <si>
     <t>C49</t>
   </si>
   <si>
-    <t>100.076mm</t>
-  </si>
-  <si>
-    <t>-57.658mm</t>
-  </si>
-  <si>
-    <t>99.531mm</t>
+    <t>66.002mm</t>
+  </si>
+  <si>
+    <t>-49.62mm</t>
+  </si>
+  <si>
+    <t>65.457mm</t>
   </si>
   <si>
     <t>C50</t>
   </si>
   <si>
-    <t>100.05mm</t>
-  </si>
-  <si>
-    <t>-58.775mm</t>
-  </si>
-  <si>
-    <t>99.505mm</t>
+    <t>74.676mm</t>
+  </si>
+  <si>
+    <t>-49.784mm</t>
+  </si>
+  <si>
+    <t>74.131mm</t>
   </si>
   <si>
     <t>C51</t>
   </si>
   <si>
-    <t>108.712mm</t>
-  </si>
-  <si>
-    <t>-58.801mm</t>
-  </si>
-  <si>
-    <t>109.257mm</t>
-  </si>
-  <si>
-    <t>C42</t>
-  </si>
-  <si>
-    <t>-48.514mm</t>
-  </si>
-  <si>
-    <t>108.167mm</t>
-  </si>
-  <si>
-    <t>C38</t>
-  </si>
-  <si>
-    <t>100.293mm</t>
-  </si>
-  <si>
-    <t>-46.826mm</t>
-  </si>
-  <si>
-    <t>-46.281mm</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>-57.785mm</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>CL05A105KA5NQNC</t>
-  </si>
-  <si>
-    <t>68.834mm</t>
-  </si>
-  <si>
-    <t>-61.341mm</t>
-  </si>
-  <si>
-    <t>69.379mm</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>86.524mm</t>
-  </si>
-  <si>
-    <t>-65.871mm</t>
-  </si>
-  <si>
-    <t>-66.416mm</t>
-  </si>
-  <si>
-    <t>C24</t>
-  </si>
-  <si>
-    <t>86.487mm</t>
-  </si>
-  <si>
-    <t>-63.5mm</t>
-  </si>
-  <si>
-    <t>-64.045mm</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>108.204mm</t>
-  </si>
-  <si>
-    <t>-81.28mm</t>
-  </si>
-  <si>
-    <t>-80.735mm</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>-61.087mm</t>
-  </si>
-  <si>
-    <t>-60.542mm</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>88.9mm</t>
-  </si>
-  <si>
-    <t>88.355mm</t>
-  </si>
-  <si>
-    <t>C43</t>
-  </si>
-  <si>
-    <t>97.626mm</t>
-  </si>
-  <si>
-    <t>-58.711mm</t>
-  </si>
-  <si>
-    <t>98.171mm</t>
-  </si>
-  <si>
-    <t>C44</t>
-  </si>
-  <si>
-    <t>C45</t>
-  </si>
-  <si>
-    <t>C40</t>
-  </si>
-  <si>
-    <t>97.536mm</t>
-  </si>
-  <si>
-    <t>96.991mm</t>
-  </si>
-  <si>
-    <t>C37</t>
-  </si>
-  <si>
-    <t>97.663mm</t>
-  </si>
-  <si>
-    <t>98.208mm</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>-48.768mm</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>CC0603JRNPO9BN120</t>
-  </si>
-  <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>78.486mm</t>
-  </si>
-  <si>
-    <t>-43.942mm</t>
-  </si>
-  <si>
-    <t>-43.242mm</t>
-  </si>
-  <si>
-    <t>12pF</t>
-  </si>
-  <si>
-    <t>C30</t>
-  </si>
-  <si>
-    <t>-41.021mm</t>
-  </si>
-  <si>
-    <t>-41.721mm</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>XL2EL89CSI-111YLC-12M</t>
-  </si>
-  <si>
-    <t>CRYSTAL-SMD_4P-L3.2-W2.5-BL</t>
-  </si>
-  <si>
-    <t>75.819mm</t>
-  </si>
-  <si>
-    <t>-42.291mm</t>
-  </si>
-  <si>
-    <t>74.969mm</t>
-  </si>
-  <si>
-    <t>-41.191mm</t>
-  </si>
-  <si>
-    <t>12MHz</t>
-  </si>
-  <si>
-    <t>C26</t>
-  </si>
-  <si>
-    <t>88.011mm</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>96.938mm</t>
-  </si>
-  <si>
-    <t>-81.19mm</t>
-  </si>
-  <si>
-    <t>-80.645mm</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>-65.913mm</t>
-  </si>
-  <si>
-    <t>-66.458mm</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>86.614mm</t>
-  </si>
-  <si>
-    <t>87.159mm</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>77.343mm</t>
-  </si>
-  <si>
-    <t>-58.928mm</t>
-  </si>
-  <si>
-    <t>76.798mm</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>77.47mm</t>
-  </si>
-  <si>
-    <t>76.925mm</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>-50.038mm</t>
-  </si>
-  <si>
-    <t>85.942mm</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>77.433mm</t>
-  </si>
-  <si>
-    <t>-48.551mm</t>
-  </si>
-  <si>
-    <t>76.888mm</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>85.725mm</t>
-  </si>
-  <si>
-    <t>-80.899mm</t>
-  </si>
-  <si>
-    <t>-80.354mm</t>
-  </si>
-  <si>
-    <t>C36</t>
-  </si>
-  <si>
-    <t>74.549mm</t>
-  </si>
-  <si>
-    <t>75.094mm</t>
-  </si>
-  <si>
-    <t>C46</t>
-  </si>
-  <si>
-    <t>74.575mm</t>
-  </si>
-  <si>
-    <t>-57.759mm</t>
-  </si>
-  <si>
-    <t>75.121mm</t>
-  </si>
-  <si>
-    <t>C47</t>
-  </si>
-  <si>
-    <t>66.003mm</t>
-  </si>
-  <si>
-    <t>65.458mm</t>
-  </si>
-  <si>
-    <t>C48</t>
-  </si>
-  <si>
-    <t>66.002mm</t>
-  </si>
-  <si>
-    <t>-49.62mm</t>
-  </si>
-  <si>
-    <t>65.457mm</t>
-  </si>
-  <si>
-    <t>C41</t>
-  </si>
-  <si>
-    <t>74.676mm</t>
-  </si>
-  <si>
-    <t>-49.784mm</t>
-  </si>
-  <si>
-    <t>74.131mm</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
     <t>65.405mm</t>
   </si>
   <si>
@@ -484,13 +484,13 @@
     <t>-58.965mm</t>
   </si>
   <si>
-    <t>C32</t>
+    <t>C52</t>
   </si>
   <si>
     <t>66.548mm</t>
   </si>
   <si>
-    <t>C3</t>
+    <t>C58</t>
   </si>
   <si>
     <t>74.967mm</t>
@@ -502,7 +502,7 @@
     <t>-80.391mm</t>
   </si>
   <si>
-    <t>D1</t>
+    <t>D2</t>
   </si>
   <si>
     <t>ESDA6V1L_C587141</t>
@@ -526,18 +526,18 @@
     <t>ESDA6V1L</t>
   </si>
   <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>92.456mm</t>
+  </si>
+  <si>
+    <t>93.406mm</t>
+  </si>
+  <si>
     <t>D4</t>
   </si>
   <si>
-    <t>92.456mm</t>
-  </si>
-  <si>
-    <t>93.406mm</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
     <t>81.28mm</t>
   </si>
   <si>
@@ -547,7 +547,7 @@
     <t>-80.28mm</t>
   </si>
   <si>
-    <t>D2</t>
+    <t>D5</t>
   </si>
   <si>
     <t>70.485mm</t>
@@ -556,27 +556,27 @@
     <t>71.435mm</t>
   </si>
   <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>SZYY0603B</t>
+  </si>
+  <si>
+    <t>LED0603-R-RD_BLUE</t>
+  </si>
+  <si>
+    <t>96.774mm</t>
+  </si>
+  <si>
+    <t>-33.02mm</t>
+  </si>
+  <si>
+    <t>-33.871mm</t>
+  </si>
+  <si>
     <t>LED3</t>
   </si>
   <si>
-    <t>SZYY0603B</t>
-  </si>
-  <si>
-    <t>LED0603-R-RD_BLUE</t>
-  </si>
-  <si>
-    <t>96.774mm</t>
-  </si>
-  <si>
-    <t>-33.02mm</t>
-  </si>
-  <si>
-    <t>-33.871mm</t>
-  </si>
-  <si>
-    <t>LED4</t>
-  </si>
-  <si>
     <t>SZYY0603G</t>
   </si>
   <si>
@@ -586,31 +586,31 @@
     <t>98.806mm</t>
   </si>
   <si>
-    <t>LED2</t>
+    <t>LED6</t>
   </si>
   <si>
     <t>94.742mm</t>
   </si>
   <si>
-    <t>LED6</t>
+    <t>LED7</t>
   </si>
   <si>
     <t>89.916mm</t>
   </si>
   <si>
-    <t>LED7</t>
+    <t>LED8</t>
   </si>
   <si>
     <t>91.821mm</t>
   </si>
   <si>
-    <t>LED5</t>
+    <t>LED9</t>
   </si>
   <si>
     <t>87.884mm</t>
   </si>
   <si>
-    <t>LED9</t>
+    <t>LED10</t>
   </si>
   <si>
     <t>82.69mm</t>
@@ -622,19 +622,19 @@
     <t>-33.845mm</t>
   </si>
   <si>
-    <t>LED10</t>
+    <t>LED11</t>
   </si>
   <si>
     <t>84.722mm</t>
   </si>
   <si>
-    <t>LED8</t>
+    <t>LED12</t>
   </si>
   <si>
     <t>80.658mm</t>
   </si>
   <si>
-    <t>LED12</t>
+    <t>LED13</t>
   </si>
   <si>
     <t>75.324mm</t>
@@ -646,16 +646,16 @@
     <t>-33.858mm</t>
   </si>
   <si>
-    <t>LED13</t>
-  </si>
-  <si>
-    <t>LED11</t>
+    <t>LED14</t>
+  </si>
+  <si>
+    <t>LED15</t>
   </si>
   <si>
     <t>73.292mm</t>
   </si>
   <si>
-    <t>R30</t>
+    <t>R5</t>
   </si>
   <si>
     <t>0402WGF1002TCE</t>
@@ -673,7 +673,7 @@
     <t>10kΩ</t>
   </si>
   <si>
-    <t>R27</t>
+    <t>R63</t>
   </si>
   <si>
     <t>105.156mm</t>
@@ -685,13 +685,13 @@
     <t>104.723mm</t>
   </si>
   <si>
-    <t>R4</t>
+    <t>R74</t>
   </si>
   <si>
     <t>0603WAF1200T5E</t>
   </si>
   <si>
-    <t>R0603_1</t>
+    <t>R0603</t>
   </si>
   <si>
     <t>101.473mm</t>
@@ -706,7 +706,7 @@
     <t>120Ω</t>
   </si>
   <si>
-    <t>R6</t>
+    <t>R75</t>
   </si>
   <si>
     <t>0603WAF0000T5E</t>
@@ -724,7 +724,7 @@
     <t>0Ω</t>
   </si>
   <si>
-    <t>R11</t>
+    <t>R76</t>
   </si>
   <si>
     <t>0603WAF1001T5E</t>
@@ -742,13 +742,13 @@
     <t>1kΩ</t>
   </si>
   <si>
-    <t>R12</t>
+    <t>R77</t>
   </si>
   <si>
     <t>94.234mm</t>
   </si>
   <si>
-    <t>R13</t>
+    <t>R78</t>
   </si>
   <si>
     <t>95.898mm</t>
@@ -760,13 +760,13 @@
     <t>-38.7mm</t>
   </si>
   <si>
-    <t>R28</t>
+    <t>R79</t>
   </si>
   <si>
     <t>98.096mm</t>
   </si>
   <si>
-    <t>R25</t>
+    <t>R80</t>
   </si>
   <si>
     <t>93.98mm</t>
@@ -778,31 +778,31 @@
     <t>93.547mm</t>
   </si>
   <si>
-    <t>R10</t>
+    <t>R85</t>
   </si>
   <si>
     <t>90.17mm</t>
   </si>
   <si>
-    <t>R14</t>
+    <t>R87</t>
   </si>
   <si>
     <t>87.757mm</t>
   </si>
   <si>
-    <t>R15</t>
+    <t>R88</t>
   </si>
   <si>
     <t>89.408mm</t>
   </si>
   <si>
-    <t>R16</t>
+    <t>R89</t>
   </si>
   <si>
     <t>91.059mm</t>
   </si>
   <si>
-    <t>R7</t>
+    <t>R90</t>
   </si>
   <si>
     <t>-49.022mm</t>
@@ -811,750 +811,780 @@
     <t>87.047mm</t>
   </si>
   <si>
+    <t>R91</t>
+  </si>
+  <si>
+    <t>82.677mm</t>
+  </si>
+  <si>
+    <t>82.244mm</t>
+  </si>
+  <si>
+    <t>R96</t>
+  </si>
+  <si>
+    <t>78.994mm</t>
+  </si>
+  <si>
+    <t>-81.788mm</t>
+  </si>
+  <si>
+    <t>-82.541mm</t>
+  </si>
+  <si>
+    <t>R98</t>
+  </si>
+  <si>
+    <t>79.375mm</t>
+  </si>
+  <si>
+    <t>R99</t>
+  </si>
+  <si>
+    <t>81.026mm</t>
+  </si>
+  <si>
+    <t>R100</t>
+  </si>
+  <si>
+    <t>82.423mm</t>
+  </si>
+  <si>
+    <t>R101</t>
+  </si>
+  <si>
+    <t>74.93mm</t>
+  </si>
+  <si>
+    <t>75.363mm</t>
+  </si>
+  <si>
+    <t>R102</t>
+  </si>
+  <si>
+    <t>70.866mm</t>
+  </si>
+  <si>
+    <t>70.433mm</t>
+  </si>
+  <si>
+    <t>R107</t>
+  </si>
+  <si>
+    <t>68.199mm</t>
+  </si>
+  <si>
+    <t>-82.169mm</t>
+  </si>
+  <si>
+    <t>-82.922mm</t>
+  </si>
+  <si>
+    <t>R109</t>
+  </si>
+  <si>
+    <t>74.295mm</t>
+  </si>
+  <si>
+    <t>R110</t>
+  </si>
+  <si>
+    <t>75.946mm</t>
+  </si>
+  <si>
+    <t>R111</t>
+  </si>
+  <si>
+    <t>77.597mm</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>VPT85BB-01A</t>
+  </si>
+  <si>
+    <t>XFMR-SMD_L7.5-W6.7-P2.54-LS7.7-BL</t>
+  </si>
+  <si>
+    <t>75.692mm</t>
+  </si>
+  <si>
+    <t>71.842mm</t>
+  </si>
+  <si>
+    <t>-60.96mm</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>98.933mm</t>
+  </si>
+  <si>
+    <t>102.783mm</t>
+  </si>
+  <si>
+    <t>-66.04mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>STM32G431C8T6</t>
+  </si>
+  <si>
+    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
+  </si>
+  <si>
+    <t>104.394mm</t>
+  </si>
+  <si>
+    <t>-53.594mm</t>
+  </si>
+  <si>
+    <t>108.644mm</t>
+  </si>
+  <si>
+    <t>-56.344mm</t>
+  </si>
+  <si>
+    <t>U20</t>
+  </si>
+  <si>
+    <t>VPS8505</t>
+  </si>
+  <si>
+    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>68.326mm</t>
+  </si>
+  <si>
+    <t>69.676mm</t>
+  </si>
+  <si>
+    <t>-64.45mm</t>
+  </si>
+  <si>
+    <t>U21</t>
+  </si>
+  <si>
+    <t>DSK36_C22466353</t>
+  </si>
+  <si>
+    <t>SOD-123FL_L2.8-W1.9-LS3.7-RD</t>
+  </si>
+  <si>
+    <t>83.312mm</t>
+  </si>
+  <si>
+    <t>85.012mm</t>
+  </si>
+  <si>
+    <t>DSK36</t>
+  </si>
+  <si>
+    <t>U22</t>
+  </si>
+  <si>
+    <t>83.439mm</t>
+  </si>
+  <si>
+    <t>-66.294mm</t>
+  </si>
+  <si>
+    <t>85.139mm</t>
+  </si>
+  <si>
+    <t>U24</t>
+  </si>
+  <si>
+    <t>TPS76350DBVR-TP</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L3.0-W1.6-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>82.162mm</t>
+  </si>
+  <si>
+    <t>-62.55mm</t>
+  </si>
+  <si>
+    <t>U25</t>
+  </si>
+  <si>
+    <t>ISO1050DWR</t>
+  </si>
+  <si>
+    <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
+  </si>
+  <si>
+    <t>-73.66mm</t>
+  </si>
+  <si>
+    <t>-68.91mm</t>
+  </si>
+  <si>
+    <t>U26</t>
+  </si>
+  <si>
+    <t>93.218mm</t>
+  </si>
+  <si>
+    <t>97.468mm</t>
+  </si>
+  <si>
+    <t>U29</t>
+  </si>
+  <si>
+    <t>107.061mm</t>
+  </si>
+  <si>
+    <t>105.711mm</t>
+  </si>
+  <si>
+    <t>U30</t>
+  </si>
+  <si>
+    <t>89.359mm</t>
+  </si>
+  <si>
+    <t>U31</t>
+  </si>
+  <si>
+    <t>91.186mm</t>
+  </si>
+  <si>
+    <t>-60.833mm</t>
+  </si>
+  <si>
+    <t>89.486mm</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t>92.336mm</t>
+  </si>
+  <si>
+    <t>U33</t>
+  </si>
+  <si>
+    <t>96.901mm</t>
+  </si>
+  <si>
+    <t>U34</t>
+  </si>
+  <si>
+    <t>81.915mm</t>
+  </si>
+  <si>
+    <t>-53.721mm</t>
+  </si>
+  <si>
+    <t>86.165mm</t>
+  </si>
+  <si>
+    <t>-56.471mm</t>
+  </si>
+  <si>
+    <t>C75</t>
+  </si>
+  <si>
+    <t>CGA0603X5R226M160JT</t>
+  </si>
+  <si>
+    <t>65.532mm</t>
+  </si>
+  <si>
+    <t>-46.355mm</t>
+  </si>
+  <si>
+    <t>-47.055mm</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>SI2301_C2891731</t>
+  </si>
+  <si>
+    <t>74.168mm</t>
+  </si>
+  <si>
+    <t>-46.228mm</t>
+  </si>
+  <si>
+    <t>73.168mm</t>
+  </si>
+  <si>
+    <t>-45.278mm</t>
+  </si>
+  <si>
+    <t>SI2301</t>
+  </si>
+  <si>
+    <t>U41</t>
+  </si>
+  <si>
+    <t>81.534mm</t>
+  </si>
+  <si>
+    <t>-73.533mm</t>
+  </si>
+  <si>
+    <t>85.979mm</t>
+  </si>
+  <si>
+    <t>-68.783mm</t>
+  </si>
+  <si>
+    <t>U42</t>
+  </si>
+  <si>
+    <t>70.231mm</t>
+  </si>
+  <si>
+    <t>74.481mm</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>SS8050_C916392</t>
+  </si>
+  <si>
+    <t>69.596mm</t>
+  </si>
+  <si>
+    <t>68.596mm</t>
+  </si>
+  <si>
+    <t>-45.405mm</t>
+  </si>
+  <si>
+    <t>SS8050</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>0603WAF1004T5E</t>
+  </si>
+  <si>
+    <t>67.183mm</t>
+  </si>
+  <si>
+    <t>-45.602mm</t>
+  </si>
+  <si>
+    <t>1MΩ</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>RCA03100KJLF</t>
+  </si>
+  <si>
+    <t>72.009mm</t>
+  </si>
+  <si>
+    <t>-45.475mm</t>
+  </si>
+  <si>
+    <t>100kΩ</t>
+  </si>
+  <si>
+    <t>TP1</t>
+  </si>
+  <si>
+    <t>Test-Point</t>
+  </si>
+  <si>
+    <t>Test-Point-0.5mm</t>
+  </si>
+  <si>
+    <t>69.5mm</t>
+  </si>
+  <si>
+    <t>-56.238mm</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>TP2</t>
+  </si>
+  <si>
+    <t>70.75mm</t>
+  </si>
+  <si>
+    <t>TP3</t>
+  </si>
+  <si>
+    <t>67mm</t>
+  </si>
+  <si>
+    <t>U49</t>
+  </si>
+  <si>
+    <t>TP4</t>
+  </si>
+  <si>
+    <t>68.25mm</t>
+  </si>
+  <si>
+    <t>TP5</t>
+  </si>
+  <si>
+    <t>92.5mm</t>
+  </si>
+  <si>
+    <t>-55.785mm</t>
+  </si>
+  <si>
+    <t>TP6</t>
+  </si>
+  <si>
+    <t>93.75mm</t>
+  </si>
+  <si>
+    <t>TP7</t>
+  </si>
+  <si>
+    <t>90mm</t>
+  </si>
+  <si>
+    <t>TP8</t>
+  </si>
+  <si>
+    <t>91.25mm</t>
+  </si>
+  <si>
+    <t>TP9</t>
+  </si>
+  <si>
+    <t>103.5mm</t>
+  </si>
+  <si>
+    <t>-56.023mm</t>
+  </si>
+  <si>
+    <t>TP10</t>
+  </si>
+  <si>
+    <t>104.75mm</t>
+  </si>
+  <si>
+    <t>TP11</t>
+  </si>
+  <si>
+    <t>101mm</t>
+  </si>
+  <si>
+    <t>C71</t>
+  </si>
+  <si>
+    <t>CL10A106MO8NQNC</t>
+  </si>
+  <si>
+    <t>84.201mm</t>
+  </si>
+  <si>
+    <t>-38.673mm</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C72</t>
+  </si>
+  <si>
+    <t>TP12</t>
+  </si>
+  <si>
+    <t>102.25mm</t>
+  </si>
+  <si>
+    <t>TP13</t>
+  </si>
+  <si>
+    <t>81mm</t>
+  </si>
+  <si>
+    <t>-56.397mm</t>
+  </si>
+  <si>
+    <t>TP14</t>
+  </si>
+  <si>
+    <t>82.25mm</t>
+  </si>
+  <si>
+    <t>TP15</t>
+  </si>
+  <si>
+    <t>78.5mm</t>
+  </si>
+  <si>
+    <t>TP16</t>
+  </si>
+  <si>
+    <t>79.75mm</t>
+  </si>
+  <si>
+    <t>C76</t>
+  </si>
+  <si>
+    <t>108.56mm</t>
+  </si>
+  <si>
+    <t>-65.636mm</t>
+  </si>
+  <si>
+    <t>108.015mm</t>
+  </si>
+  <si>
+    <t>C77</t>
+  </si>
+  <si>
+    <t>105.918mm</t>
+  </si>
+  <si>
+    <t>-65.659mm</t>
+  </si>
+  <si>
+    <t>105.373mm</t>
+  </si>
+  <si>
+    <t>C78</t>
+  </si>
+  <si>
+    <t>68.961mm</t>
+  </si>
+  <si>
+    <t>-65.786mm</t>
+  </si>
+  <si>
+    <t>69.506mm</t>
+  </si>
+  <si>
+    <t>C79</t>
+  </si>
+  <si>
+    <t>66.294mm</t>
+  </si>
+  <si>
+    <t>65.749mm</t>
+  </si>
+  <si>
+    <t>U52</t>
+  </si>
+  <si>
+    <t>SM02B-GHS-TB(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-SMD_SM02B-GHS-TB-LF-SN</t>
+  </si>
+  <si>
+    <t>-86.995mm</t>
+  </si>
+  <si>
+    <t>98.181mm</t>
+  </si>
+  <si>
+    <t>-85.395mm</t>
+  </si>
+  <si>
+    <t>U53</t>
+  </si>
+  <si>
+    <t>90.932mm</t>
+  </si>
+  <si>
+    <t>-87.122mm</t>
+  </si>
+  <si>
+    <t>90.307mm</t>
+  </si>
+  <si>
+    <t>-85.522mm</t>
+  </si>
+  <si>
+    <t>U54</t>
+  </si>
+  <si>
+    <t>83.058mm</t>
+  </si>
+  <si>
+    <t>82.433mm</t>
+  </si>
+  <si>
+    <t>U55</t>
+  </si>
+  <si>
+    <t>74.305mm</t>
+  </si>
+  <si>
+    <t>U56</t>
+  </si>
+  <si>
+    <t>TLV75733PDBVR</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L2.9-W1.6-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>-45.212mm</t>
+  </si>
+  <si>
+    <t>95.184mm</t>
+  </si>
+  <si>
+    <t>-44.112mm</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>SMBJ6.0CA_C113977</t>
+  </si>
+  <si>
+    <t>SMB_L4.6-W3.6-LS5.3-BI</t>
+  </si>
+  <si>
+    <t>97.79mm</t>
+  </si>
+  <si>
+    <t>-43.688mm</t>
+  </si>
+  <si>
+    <t>-46.279mm</t>
+  </si>
+  <si>
+    <t>SMBJ6.0CA</t>
+  </si>
+  <si>
+    <t>CS1</t>
+  </si>
+  <si>
+    <t>106.045mm</t>
+  </si>
+  <si>
+    <t>CS2</t>
+  </si>
+  <si>
+    <t>CS3</t>
+  </si>
+  <si>
+    <t>83.566mm</t>
+  </si>
+  <si>
+    <t>CS4</t>
+  </si>
+  <si>
+    <t>72.771mm</t>
+  </si>
+  <si>
+    <t>C61</t>
+  </si>
+  <si>
+    <t>93.091mm</t>
+  </si>
+  <si>
+    <t>-40.894mm</t>
+  </si>
+  <si>
+    <t>-40.194mm</t>
+  </si>
+  <si>
+    <t>C62</t>
+  </si>
+  <si>
+    <t>99.06mm</t>
+  </si>
+  <si>
+    <t>-37.846mm</t>
+  </si>
+  <si>
+    <t>-38.546mm</t>
+  </si>
+  <si>
+    <t>C63</t>
+  </si>
+  <si>
+    <t>06035C104JAT2A</t>
+  </si>
+  <si>
+    <t>C64</t>
+  </si>
+  <si>
+    <t>97.409mm</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>FSMD100-1206R</t>
+  </si>
+  <si>
+    <t>F1206</t>
+  </si>
+  <si>
+    <t>100.838mm</t>
+  </si>
+  <si>
+    <t>-40.005mm</t>
+  </si>
+  <si>
+    <t>-38.56mm</t>
+  </si>
+  <si>
+    <t>LED16</t>
+  </si>
+  <si>
+    <t>NCD0603Y2</t>
+  </si>
+  <si>
+    <t>LED0603-RD</t>
+  </si>
+  <si>
+    <t>105.41mm</t>
+  </si>
+  <si>
+    <t>-47.371mm</t>
+  </si>
+  <si>
+    <t>106.159mm</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>0603WAF2001T5E</t>
+  </si>
+  <si>
+    <t>101.727mm</t>
+  </si>
+  <si>
+    <t>-46.863mm</t>
+  </si>
+  <si>
+    <t>-46.11mm</t>
+  </si>
+  <si>
+    <t>2kΩ</t>
+  </si>
+  <si>
     <t>R2</t>
   </si>
   <si>
-    <t>82.677mm</t>
-  </si>
-  <si>
-    <t>82.244mm</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>78.994mm</t>
-  </si>
-  <si>
-    <t>-81.788mm</t>
-  </si>
-  <si>
-    <t>-82.541mm</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>79.375mm</t>
-  </si>
-  <si>
-    <t>R18</t>
-  </si>
-  <si>
-    <t>81.026mm</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>82.423mm</t>
-  </si>
-  <si>
-    <t>R29</t>
-  </si>
-  <si>
-    <t>74.93mm</t>
-  </si>
-  <si>
-    <t>75.363mm</t>
-  </si>
-  <si>
-    <t>R26</t>
-  </si>
-  <si>
-    <t>70.866mm</t>
-  </si>
-  <si>
-    <t>70.433mm</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>68.199mm</t>
-  </si>
-  <si>
-    <t>-82.169mm</t>
-  </si>
-  <si>
-    <t>-82.922mm</t>
-  </si>
-  <si>
-    <t>R22</t>
-  </si>
-  <si>
-    <t>74.295mm</t>
-  </si>
-  <si>
-    <t>R23</t>
-  </si>
-  <si>
-    <t>75.946mm</t>
-  </si>
-  <si>
-    <t>R24</t>
-  </si>
-  <si>
-    <t>77.597mm</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>VPT85BB-01A</t>
-  </si>
-  <si>
-    <t>XFMR-SMD_L7.5-W6.7-P2.54-LS7.7-BL</t>
-  </si>
-  <si>
-    <t>75.692mm</t>
-  </si>
-  <si>
-    <t>71.842mm</t>
-  </si>
-  <si>
-    <t>-60.96mm</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>98.933mm</t>
-  </si>
-  <si>
-    <t>102.783mm</t>
-  </si>
-  <si>
-    <t>-66.04mm</t>
-  </si>
-  <si>
-    <t>U18</t>
-  </si>
-  <si>
-    <t>STM32G431C8T6</t>
-  </si>
-  <si>
-    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
-  </si>
-  <si>
-    <t>104.394mm</t>
-  </si>
-  <si>
-    <t>-53.594mm</t>
-  </si>
-  <si>
-    <t>108.644mm</t>
-  </si>
-  <si>
-    <t>-56.344mm</t>
-  </si>
-  <si>
-    <t>U9</t>
-  </si>
-  <si>
-    <t>VPS8505</t>
-  </si>
-  <si>
-    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>68.326mm</t>
-  </si>
-  <si>
-    <t>69.676mm</t>
-  </si>
-  <si>
-    <t>-64.45mm</t>
-  </si>
-  <si>
-    <t>U7</t>
-  </si>
-  <si>
-    <t>DSK36_C22466353</t>
-  </si>
-  <si>
-    <t>SOD-123FL_L2.8-W1.9-LS3.7-RD</t>
-  </si>
-  <si>
-    <t>83.312mm</t>
-  </si>
-  <si>
-    <t>85.012mm</t>
-  </si>
-  <si>
-    <t>DSK36</t>
-  </si>
-  <si>
-    <t>U11</t>
-  </si>
-  <si>
-    <t>83.439mm</t>
-  </si>
-  <si>
-    <t>-66.294mm</t>
-  </si>
-  <si>
-    <t>85.139mm</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>TPS76350DBVR-TP</t>
-  </si>
-  <si>
-    <t>SOT-23-5_L3.0-W1.6-P0.95-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>82.162mm</t>
-  </si>
-  <si>
-    <t>-62.55mm</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>ISO1050DWR</t>
-  </si>
-  <si>
-    <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
-  </si>
-  <si>
-    <t>-73.66mm</t>
-  </si>
-  <si>
-    <t>-68.91mm</t>
-  </si>
-  <si>
-    <t>U16</t>
-  </si>
-  <si>
-    <t>93.218mm</t>
-  </si>
-  <si>
-    <t>97.468mm</t>
-  </si>
-  <si>
-    <t>U14</t>
-  </si>
-  <si>
-    <t>107.061mm</t>
-  </si>
-  <si>
-    <t>105.711mm</t>
-  </si>
-  <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>89.359mm</t>
-  </si>
-  <si>
-    <t>U15</t>
-  </si>
-  <si>
-    <t>91.186mm</t>
-  </si>
-  <si>
-    <t>-60.833mm</t>
-  </si>
-  <si>
-    <t>89.486mm</t>
-  </si>
-  <si>
-    <t>U13</t>
-  </si>
-  <si>
-    <t>92.336mm</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>96.901mm</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>81.915mm</t>
-  </si>
-  <si>
-    <t>-53.721mm</t>
-  </si>
-  <si>
-    <t>86.165mm</t>
-  </si>
-  <si>
-    <t>-56.471mm</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>CGA0603X5R226M160JT</t>
-  </si>
-  <si>
-    <t>65.532mm</t>
-  </si>
-  <si>
-    <t>-46.355mm</t>
-  </si>
-  <si>
-    <t>-47.055mm</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>SI2301_C2891731</t>
-  </si>
-  <si>
-    <t>74.168mm</t>
-  </si>
-  <si>
-    <t>-46.228mm</t>
-  </si>
-  <si>
-    <t>73.168mm</t>
-  </si>
-  <si>
-    <t>-45.278mm</t>
-  </si>
-  <si>
-    <t>SI2301</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>81.534mm</t>
-  </si>
-  <si>
-    <t>-73.533mm</t>
-  </si>
-  <si>
-    <t>85.979mm</t>
-  </si>
-  <si>
-    <t>-68.783mm</t>
-  </si>
-  <si>
-    <t>U17</t>
-  </si>
-  <si>
-    <t>70.231mm</t>
-  </si>
-  <si>
-    <t>74.481mm</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>SS8050_C916392</t>
-  </si>
-  <si>
-    <t>69.596mm</t>
-  </si>
-  <si>
-    <t>68.596mm</t>
-  </si>
-  <si>
-    <t>-45.405mm</t>
-  </si>
-  <si>
-    <t>SS8050</t>
-  </si>
-  <si>
-    <t>R19</t>
-  </si>
-  <si>
-    <t>0603WAF1004T5E</t>
-  </si>
-  <si>
-    <t>67.183mm</t>
-  </si>
-  <si>
-    <t>-45.602mm</t>
-  </si>
-  <si>
-    <t>1MΩ</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>RCA03100KJLF</t>
-  </si>
-  <si>
-    <t>72.009mm</t>
-  </si>
-  <si>
-    <t>-45.475mm</t>
-  </si>
-  <si>
-    <t>100kΩ</t>
-  </si>
-  <si>
-    <t>TP7</t>
-  </si>
-  <si>
-    <t>Test-Point</t>
-  </si>
-  <si>
-    <t>Test-Point-0.5mm</t>
-  </si>
-  <si>
-    <t>69.5mm</t>
-  </si>
-  <si>
-    <t>-56.238mm</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>TP10</t>
-  </si>
-  <si>
-    <t>70.75mm</t>
-  </si>
-  <si>
-    <t>TP14</t>
-  </si>
-  <si>
-    <t>67mm</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>TP16</t>
-  </si>
-  <si>
-    <t>68.25mm</t>
-  </si>
-  <si>
-    <t>TP6</t>
-  </si>
-  <si>
-    <t>92.5mm</t>
-  </si>
-  <si>
-    <t>-55.785mm</t>
-  </si>
-  <si>
-    <t>TP9</t>
-  </si>
-  <si>
-    <t>93.75mm</t>
-  </si>
-  <si>
-    <t>TP12</t>
-  </si>
-  <si>
-    <t>90mm</t>
-  </si>
-  <si>
-    <t>TP15</t>
-  </si>
-  <si>
-    <t>91.25mm</t>
-  </si>
-  <si>
-    <t>TP5</t>
-  </si>
-  <si>
-    <t>103.5mm</t>
-  </si>
-  <si>
-    <t>-56.023mm</t>
-  </si>
-  <si>
-    <t>TP8</t>
-  </si>
-  <si>
-    <t>104.75mm</t>
-  </si>
-  <si>
-    <t>TP11</t>
-  </si>
-  <si>
-    <t>101mm</t>
-  </si>
-  <si>
-    <t>TP13</t>
-  </si>
-  <si>
-    <t>102.25mm</t>
-  </si>
-  <si>
-    <t>TP1</t>
-  </si>
-  <si>
-    <t>81mm</t>
-  </si>
-  <si>
-    <t>-56.397mm</t>
-  </si>
-  <si>
-    <t>TP2</t>
-  </si>
-  <si>
-    <t>82.25mm</t>
-  </si>
-  <si>
-    <t>TP3</t>
-  </si>
-  <si>
-    <t>78.5mm</t>
-  </si>
-  <si>
-    <t>TP4</t>
-  </si>
-  <si>
-    <t>79.75mm</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>108.56mm</t>
-  </si>
-  <si>
-    <t>-65.636mm</t>
-  </si>
-  <si>
-    <t>108.015mm</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>105.918mm</t>
-  </si>
-  <si>
-    <t>-65.659mm</t>
-  </si>
-  <si>
-    <t>105.373mm</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>68.961mm</t>
-  </si>
-  <si>
-    <t>-65.786mm</t>
-  </si>
-  <si>
-    <t>69.506mm</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>66.294mm</t>
-  </si>
-  <si>
-    <t>65.749mm</t>
-  </si>
-  <si>
-    <t>U19</t>
-  </si>
-  <si>
-    <t>SM02B-GHS-TB(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-SMD_SM02B-GHS-TB-LF-SN</t>
-  </si>
-  <si>
-    <t>-86.995mm</t>
-  </si>
-  <si>
-    <t>98.181mm</t>
-  </si>
-  <si>
-    <t>-85.395mm</t>
-  </si>
-  <si>
-    <t>U20</t>
-  </si>
-  <si>
-    <t>90.932mm</t>
-  </si>
-  <si>
-    <t>-87.122mm</t>
-  </si>
-  <si>
-    <t>90.307mm</t>
-  </si>
-  <si>
-    <t>-85.522mm</t>
-  </si>
-  <si>
-    <t>U21</t>
-  </si>
-  <si>
-    <t>83.058mm</t>
-  </si>
-  <si>
-    <t>82.433mm</t>
-  </si>
-  <si>
-    <t>U22</t>
-  </si>
-  <si>
-    <t>74.305mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>TLV75733PDBVR</t>
-  </si>
-  <si>
-    <t>SOT-23-5_L2.9-W1.6-P0.95-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>-45.212mm</t>
-  </si>
-  <si>
-    <t>95.184mm</t>
-  </si>
-  <si>
-    <t>-44.112mm</t>
-  </si>
-  <si>
-    <t>CS1</t>
-  </si>
-  <si>
-    <t>106.045mm</t>
-  </si>
-  <si>
-    <t>CS4</t>
-  </si>
-  <si>
-    <t>CS3</t>
-  </si>
-  <si>
-    <t>83.566mm</t>
-  </si>
-  <si>
-    <t>CS2</t>
-  </si>
-  <si>
-    <t>72.771mm</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>CL10A106MO8NQNC</t>
-  </si>
-  <si>
-    <t>93.091mm</t>
-  </si>
-  <si>
-    <t>-40.894mm</t>
-  </si>
-  <si>
-    <t>-40.194mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>99.06mm</t>
-  </si>
-  <si>
-    <t>-37.846mm</t>
-  </si>
-  <si>
-    <t>-38.546mm</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>06035C104JAT2A</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>97.409mm</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>FSMD100-1206R</t>
-  </si>
-  <si>
-    <t>F1206</t>
-  </si>
-  <si>
-    <t>100.838mm</t>
-  </si>
-  <si>
-    <t>-40.005mm</t>
-  </si>
-  <si>
-    <t>-38.56mm</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>NCD0603Y2</t>
-  </si>
-  <si>
-    <t>LED0603-RD</t>
-  </si>
-  <si>
-    <t>105.41mm</t>
-  </si>
-  <si>
-    <t>-47.371mm</t>
-  </si>
-  <si>
-    <t>106.159mm</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>0603WAF2001T5E</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>101.727mm</t>
-  </si>
-  <si>
-    <t>-46.863mm</t>
-  </si>
-  <si>
-    <t>-46.11mm</t>
-  </si>
-  <si>
-    <t>2kΩ</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
     <t>TNPW06035K10BEEA</t>
   </si>
   <si>
@@ -1564,7 +1594,7 @@
     <t>-36.182mm</t>
   </si>
   <si>
-    <t>-35.428mm</t>
+    <t>-36.935mm</t>
   </si>
   <si>
     <t>5.1kΩ</t>
@@ -1582,7 +1612,7 @@
     <t>-44.792mm</t>
   </si>
   <si>
-    <t>U10</t>
+    <t>U50</t>
   </si>
   <si>
     <t>SL2.1A</t>
@@ -1603,7 +1633,7 @@
     <t>-46.052mm</t>
   </si>
   <si>
-    <t>USB1</t>
+    <t>USB9</t>
   </si>
   <si>
     <t>TYPEC-304-BCP16_C720629</t>
@@ -1625,27 +1655,6 @@
   </si>
   <si>
     <t>TYPEC-304-BCP16</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>SMBJ6.0CA_C113977</t>
-  </si>
-  <si>
-    <t>SMB_L4.6-W3.6-LS5.3-BI</t>
-  </si>
-  <si>
-    <t>97.79mm</t>
-  </si>
-  <si>
-    <t>-43.688mm</t>
-  </si>
-  <si>
-    <t>-46.079mm</t>
-  </si>
-  <si>
-    <t>SMBJ6.0CA</t>
   </si>
 </sst>
 </file>
@@ -2022,7 +2031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O149"/>
+  <dimension ref="A1:O151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -3050,7 +3059,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M22" t="s">
         <v>22</v>
@@ -7626,98 +7635,98 @@
         <v>425</v>
       </c>
       <c r="B120" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="C120" t="s">
-        <v>398</v>
+        <v>86</v>
       </c>
       <c r="D120" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E120" t="s">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="F120" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G120" t="s">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="H120" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I120" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="J120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="L120">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M120" t="s">
         <v>22</v>
       </c>
       <c r="N120" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="O120" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B121" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="C121" t="s">
-        <v>398</v>
+        <v>86</v>
       </c>
       <c r="D121" t="s">
+        <v>375</v>
+      </c>
+      <c r="E121" t="s">
+        <v>240</v>
+      </c>
+      <c r="F121" t="s">
+        <v>375</v>
+      </c>
+      <c r="G121" t="s">
+        <v>240</v>
+      </c>
+      <c r="H121" t="s">
+        <v>375</v>
+      </c>
+      <c r="I121" t="s">
         <v>428</v>
       </c>
-      <c r="E121" t="s">
+      <c r="J121">
+        <v>2</v>
+      </c>
+      <c r="K121" t="s">
+        <v>21</v>
+      </c>
+      <c r="L121">
+        <v>90</v>
+      </c>
+      <c r="M121" t="s">
+        <v>22</v>
+      </c>
+      <c r="N121" t="s">
         <v>429</v>
       </c>
-      <c r="F121" t="s">
-        <v>428</v>
-      </c>
-      <c r="G121" t="s">
+      <c r="O121" t="s">
         <v>429</v>
-      </c>
-      <c r="H121" t="s">
-        <v>428</v>
-      </c>
-      <c r="I121" t="s">
-        <v>429</v>
-      </c>
-      <c r="J121">
-        <v>1</v>
-      </c>
-      <c r="K121" t="s">
-        <v>401</v>
-      </c>
-      <c r="L121">
-        <v>270</v>
-      </c>
-      <c r="M121" t="s">
-        <v>22</v>
-      </c>
-      <c r="N121" t="s">
-        <v>397</v>
-      </c>
-      <c r="O121" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B122" t="s">
         <v>397</v>
@@ -7726,22 +7735,22 @@
         <v>398</v>
       </c>
       <c r="D122" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E122" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="F122" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G122" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="H122" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I122" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="J122">
         <v>1</v>
@@ -7764,7 +7773,7 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B123" t="s">
         <v>397</v>
@@ -7773,22 +7782,22 @@
         <v>398</v>
       </c>
       <c r="D123" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E123" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F123" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G123" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="H123" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I123" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="J123">
         <v>1</v>
@@ -7811,7 +7820,7 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B124" t="s">
         <v>397</v>
@@ -7820,22 +7829,22 @@
         <v>398</v>
       </c>
       <c r="D124" t="s">
+        <v>437</v>
+      </c>
+      <c r="E124" t="s">
         <v>435</v>
       </c>
-      <c r="E124" t="s">
-        <v>429</v>
-      </c>
       <c r="F124" t="s">
+        <v>437</v>
+      </c>
+      <c r="G124" t="s">
         <v>435</v>
       </c>
-      <c r="G124" t="s">
-        <v>429</v>
-      </c>
       <c r="H124" t="s">
+        <v>437</v>
+      </c>
+      <c r="I124" t="s">
         <v>435</v>
-      </c>
-      <c r="I124" t="s">
-        <v>429</v>
       </c>
       <c r="J124">
         <v>1</v>
@@ -7858,49 +7867,49 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>397</v>
       </c>
       <c r="C125" t="s">
-        <v>17</v>
+        <v>398</v>
       </c>
       <c r="D125" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E125" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F125" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G125" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H125" t="s">
         <v>439</v>
       </c>
       <c r="I125" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="J125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K125" t="s">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="L125">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M125" t="s">
         <v>22</v>
       </c>
       <c r="N125" t="s">
-        <v>23</v>
+        <v>397</v>
       </c>
       <c r="O125" t="s">
-        <v>23</v>
+        <v>397</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
@@ -7908,51 +7917,51 @@
         <v>440</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>397</v>
       </c>
       <c r="C126" t="s">
-        <v>17</v>
+        <v>398</v>
       </c>
       <c r="D126" t="s">
         <v>441</v>
       </c>
       <c r="E126" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F126" t="s">
         <v>441</v>
       </c>
       <c r="G126" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="H126" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I126" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="J126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="L126">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M126" t="s">
         <v>22</v>
       </c>
       <c r="N126" t="s">
-        <v>23</v>
+        <v>397</v>
       </c>
       <c r="O126" t="s">
-        <v>23</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B127" t="s">
         <v>16</v>
@@ -7961,22 +7970,22 @@
         <v>17</v>
       </c>
       <c r="D127" t="s">
+        <v>443</v>
+      </c>
+      <c r="E127" t="s">
+        <v>444</v>
+      </c>
+      <c r="F127" t="s">
+        <v>443</v>
+      </c>
+      <c r="G127" t="s">
+        <v>444</v>
+      </c>
+      <c r="H127" t="s">
         <v>445</v>
       </c>
-      <c r="E127" t="s">
-        <v>446</v>
-      </c>
-      <c r="F127" t="s">
-        <v>445</v>
-      </c>
-      <c r="G127" t="s">
-        <v>446</v>
-      </c>
-      <c r="H127" t="s">
-        <v>447</v>
-      </c>
       <c r="I127" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J127">
         <v>2</v>
@@ -7985,7 +7994,7 @@
         <v>21</v>
       </c>
       <c r="L127">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M127" t="s">
         <v>22</v>
@@ -7999,7 +8008,7 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B128" t="s">
         <v>16</v>
@@ -8008,22 +8017,22 @@
         <v>17</v>
       </c>
       <c r="D128" t="s">
+        <v>447</v>
+      </c>
+      <c r="E128" t="s">
+        <v>448</v>
+      </c>
+      <c r="F128" t="s">
+        <v>447</v>
+      </c>
+      <c r="G128" t="s">
+        <v>448</v>
+      </c>
+      <c r="H128" t="s">
         <v>449</v>
       </c>
-      <c r="E128" t="s">
-        <v>446</v>
-      </c>
-      <c r="F128" t="s">
-        <v>449</v>
-      </c>
-      <c r="G128" t="s">
-        <v>446</v>
-      </c>
-      <c r="H128" t="s">
-        <v>450</v>
-      </c>
       <c r="I128" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J128">
         <v>2</v>
@@ -8046,81 +8055,81 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>450</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" t="s">
         <v>451</v>
       </c>
-      <c r="B129" t="s">
+      <c r="E129" t="s">
         <v>452</v>
       </c>
-      <c r="C129" t="s">
+      <c r="F129" t="s">
+        <v>451</v>
+      </c>
+      <c r="G129" t="s">
+        <v>452</v>
+      </c>
+      <c r="H129" t="s">
         <v>453</v>
       </c>
-      <c r="D129" t="s">
-        <v>190</v>
-      </c>
-      <c r="E129" t="s">
-        <v>454</v>
-      </c>
-      <c r="F129" t="s">
-        <v>190</v>
-      </c>
-      <c r="G129" t="s">
-        <v>454</v>
-      </c>
-      <c r="H129" t="s">
-        <v>455</v>
-      </c>
       <c r="I129" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K129" t="s">
         <v>21</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M129" t="s">
         <v>22</v>
       </c>
       <c r="N129" t="s">
-        <v>452</v>
+        <v>23</v>
       </c>
       <c r="O129" t="s">
-        <v>452</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" t="s">
+        <v>455</v>
+      </c>
+      <c r="E130" t="s">
         <v>452</v>
       </c>
-      <c r="C130" t="s">
-        <v>453</v>
-      </c>
-      <c r="D130" t="s">
-        <v>458</v>
-      </c>
-      <c r="E130" t="s">
-        <v>459</v>
-      </c>
       <c r="F130" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G130" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="H130" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="I130" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="J130">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K130" t="s">
         <v>21</v>
@@ -8132,39 +8141,39 @@
         <v>22</v>
       </c>
       <c r="N130" t="s">
-        <v>452</v>
+        <v>23</v>
       </c>
       <c r="O130" t="s">
-        <v>452</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>457</v>
+      </c>
+      <c r="B131" t="s">
+        <v>458</v>
+      </c>
+      <c r="C131" t="s">
+        <v>459</v>
+      </c>
+      <c r="D131" t="s">
+        <v>190</v>
+      </c>
+      <c r="E131" t="s">
+        <v>460</v>
+      </c>
+      <c r="F131" t="s">
+        <v>190</v>
+      </c>
+      <c r="G131" t="s">
+        <v>460</v>
+      </c>
+      <c r="H131" t="s">
+        <v>461</v>
+      </c>
+      <c r="I131" t="s">
         <v>462</v>
-      </c>
-      <c r="B131" t="s">
-        <v>452</v>
-      </c>
-      <c r="C131" t="s">
-        <v>453</v>
-      </c>
-      <c r="D131" t="s">
-        <v>463</v>
-      </c>
-      <c r="E131" t="s">
-        <v>459</v>
-      </c>
-      <c r="F131" t="s">
-        <v>463</v>
-      </c>
-      <c r="G131" t="s">
-        <v>459</v>
-      </c>
-      <c r="H131" t="s">
-        <v>464</v>
-      </c>
-      <c r="I131" t="s">
-        <v>461</v>
       </c>
       <c r="J131">
         <v>4</v>
@@ -8179,39 +8188,39 @@
         <v>22</v>
       </c>
       <c r="N131" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="O131" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>463</v>
+      </c>
+      <c r="B132" t="s">
+        <v>458</v>
+      </c>
+      <c r="C132" t="s">
+        <v>459</v>
+      </c>
+      <c r="D132" t="s">
+        <v>464</v>
+      </c>
+      <c r="E132" t="s">
         <v>465</v>
       </c>
-      <c r="B132" t="s">
-        <v>452</v>
-      </c>
-      <c r="C132" t="s">
-        <v>453</v>
-      </c>
-      <c r="D132" t="s">
-        <v>280</v>
-      </c>
-      <c r="E132" t="s">
-        <v>459</v>
-      </c>
       <c r="F132" t="s">
-        <v>280</v>
+        <v>464</v>
       </c>
       <c r="G132" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="H132" t="s">
         <v>466</v>
       </c>
       <c r="I132" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="J132">
         <v>4</v>
@@ -8226,180 +8235,180 @@
         <v>22</v>
       </c>
       <c r="N132" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="O132" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>468</v>
+      </c>
+      <c r="B133" t="s">
+        <v>458</v>
+      </c>
+      <c r="C133" t="s">
+        <v>459</v>
+      </c>
+      <c r="D133" t="s">
+        <v>469</v>
+      </c>
+      <c r="E133" t="s">
+        <v>465</v>
+      </c>
+      <c r="F133" t="s">
+        <v>469</v>
+      </c>
+      <c r="G133" t="s">
+        <v>465</v>
+      </c>
+      <c r="H133" t="s">
+        <v>470</v>
+      </c>
+      <c r="I133" t="s">
         <v>467</v>
       </c>
-      <c r="B133" t="s">
-        <v>468</v>
-      </c>
-      <c r="C133" t="s">
-        <v>469</v>
-      </c>
-      <c r="D133" t="s">
-        <v>244</v>
-      </c>
-      <c r="E133" t="s">
-        <v>470</v>
-      </c>
-      <c r="F133" t="s">
-        <v>244</v>
-      </c>
-      <c r="G133" t="s">
-        <v>470</v>
-      </c>
-      <c r="H133" t="s">
-        <v>471</v>
-      </c>
-      <c r="I133" t="s">
-        <v>472</v>
-      </c>
       <c r="J133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K133" t="s">
         <v>21</v>
       </c>
       <c r="L133">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M133" t="s">
         <v>22</v>
       </c>
       <c r="N133" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="O133" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B134" t="s">
-        <v>232</v>
+        <v>458</v>
       </c>
       <c r="C134" t="s">
-        <v>226</v>
+        <v>459</v>
       </c>
       <c r="D134" t="s">
-        <v>474</v>
+        <v>280</v>
       </c>
       <c r="E134" t="s">
-        <v>271</v>
+        <v>465</v>
       </c>
       <c r="F134" t="s">
-        <v>474</v>
+        <v>280</v>
       </c>
       <c r="G134" t="s">
-        <v>271</v>
+        <v>465</v>
       </c>
       <c r="H134" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I134" t="s">
-        <v>272</v>
+        <v>467</v>
       </c>
       <c r="J134">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K134" t="s">
         <v>21</v>
       </c>
       <c r="L134">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M134" t="s">
         <v>22</v>
       </c>
       <c r="N134" t="s">
-        <v>236</v>
+        <v>458</v>
       </c>
       <c r="O134" t="s">
-        <v>236</v>
+        <v>458</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>473</v>
+      </c>
+      <c r="B135" t="s">
+        <v>474</v>
+      </c>
+      <c r="C135" t="s">
         <v>475</v>
       </c>
-      <c r="B135" t="s">
-        <v>232</v>
-      </c>
-      <c r="C135" t="s">
-        <v>226</v>
-      </c>
       <c r="D135" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="E135" t="s">
-        <v>228</v>
+        <v>476</v>
       </c>
       <c r="F135" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="G135" t="s">
-        <v>228</v>
+        <v>476</v>
       </c>
       <c r="H135" t="s">
-        <v>192</v>
+        <v>477</v>
       </c>
       <c r="I135" t="s">
-        <v>229</v>
+        <v>478</v>
       </c>
       <c r="J135">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K135" t="s">
         <v>21</v>
       </c>
       <c r="L135">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M135" t="s">
         <v>22</v>
       </c>
       <c r="N135" t="s">
-        <v>236</v>
+        <v>474</v>
       </c>
       <c r="O135" t="s">
-        <v>236</v>
+        <v>474</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B136" t="s">
-        <v>232</v>
+        <v>480</v>
       </c>
       <c r="C136" t="s">
-        <v>226</v>
+        <v>481</v>
       </c>
       <c r="D136" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E136" t="s">
-        <v>271</v>
+        <v>483</v>
       </c>
       <c r="F136" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="G136" t="s">
-        <v>271</v>
+        <v>483</v>
       </c>
       <c r="H136" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="I136" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="J136">
         <v>2</v>
@@ -8414,15 +8423,15 @@
         <v>22</v>
       </c>
       <c r="N136" t="s">
-        <v>236</v>
+        <v>485</v>
       </c>
       <c r="O136" t="s">
-        <v>236</v>
+        <v>485</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="B137" t="s">
         <v>232</v>
@@ -8431,22 +8440,22 @@
         <v>226</v>
       </c>
       <c r="D137" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E137" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="F137" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="G137" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="H137" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="I137" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="J137">
         <v>2</v>
@@ -8469,31 +8478,31 @@
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B138" t="s">
-        <v>481</v>
+        <v>232</v>
       </c>
       <c r="C138" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="D138" t="s">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="E138" t="s">
-        <v>483</v>
+        <v>228</v>
       </c>
       <c r="F138" t="s">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="G138" t="s">
-        <v>483</v>
+        <v>228</v>
       </c>
       <c r="H138" t="s">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="I138" t="s">
-        <v>484</v>
+        <v>229</v>
       </c>
       <c r="J138">
         <v>2</v>
@@ -8502,45 +8511,45 @@
         <v>21</v>
       </c>
       <c r="L138">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M138" t="s">
         <v>22</v>
       </c>
       <c r="N138" t="s">
-        <v>485</v>
+        <v>236</v>
       </c>
       <c r="O138" t="s">
-        <v>485</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B139" t="s">
-        <v>481</v>
+        <v>232</v>
       </c>
       <c r="C139" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="D139" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E139" t="s">
-        <v>488</v>
+        <v>271</v>
       </c>
       <c r="F139" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G139" t="s">
-        <v>488</v>
+        <v>271</v>
       </c>
       <c r="H139" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="I139" t="s">
-        <v>489</v>
+        <v>272</v>
       </c>
       <c r="J139">
         <v>2</v>
@@ -8555,39 +8564,39 @@
         <v>22</v>
       </c>
       <c r="N139" t="s">
-        <v>485</v>
+        <v>236</v>
       </c>
       <c r="O139" t="s">
-        <v>485</v>
+        <v>236</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B140" t="s">
-        <v>491</v>
+        <v>232</v>
       </c>
       <c r="C140" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="D140" t="s">
-        <v>192</v>
+        <v>492</v>
       </c>
       <c r="E140" t="s">
-        <v>483</v>
+        <v>287</v>
       </c>
       <c r="F140" t="s">
-        <v>192</v>
+        <v>492</v>
       </c>
       <c r="G140" t="s">
-        <v>483</v>
+        <v>287</v>
       </c>
       <c r="H140" t="s">
-        <v>192</v>
+        <v>492</v>
       </c>
       <c r="I140" t="s">
-        <v>484</v>
+        <v>288</v>
       </c>
       <c r="J140">
         <v>2</v>
@@ -8596,45 +8605,45 @@
         <v>21</v>
       </c>
       <c r="L140">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M140" t="s">
         <v>22</v>
       </c>
       <c r="N140" t="s">
-        <v>23</v>
+        <v>236</v>
       </c>
       <c r="O140" t="s">
-        <v>23</v>
+        <v>236</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B141" t="s">
-        <v>491</v>
+        <v>426</v>
       </c>
       <c r="C141" t="s">
         <v>86</v>
       </c>
       <c r="D141" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E141" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F141" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G141" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="H141" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I141" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="J141">
         <v>2</v>
@@ -8643,45 +8652,45 @@
         <v>21</v>
       </c>
       <c r="L141">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M141" t="s">
         <v>22</v>
       </c>
       <c r="N141" t="s">
-        <v>23</v>
+        <v>429</v>
       </c>
       <c r="O141" t="s">
-        <v>23</v>
+        <v>429</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B142" t="s">
-        <v>495</v>
+        <v>426</v>
       </c>
       <c r="C142" t="s">
-        <v>496</v>
+        <v>86</v>
       </c>
       <c r="D142" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E142" t="s">
+        <v>499</v>
+      </c>
+      <c r="F142" t="s">
         <v>498</v>
       </c>
-      <c r="F142" t="s">
-        <v>497</v>
-      </c>
       <c r="G142" t="s">
+        <v>499</v>
+      </c>
+      <c r="H142" t="s">
         <v>498</v>
       </c>
-      <c r="H142" t="s">
-        <v>497</v>
-      </c>
       <c r="I142" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J142">
         <v>2</v>
@@ -8690,45 +8699,45 @@
         <v>21</v>
       </c>
       <c r="L142">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M142" t="s">
         <v>22</v>
       </c>
       <c r="N142" t="s">
-        <v>495</v>
+        <v>429</v>
       </c>
       <c r="O142" t="s">
-        <v>495</v>
+        <v>429</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B143" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C143" t="s">
-        <v>502</v>
+        <v>86</v>
       </c>
       <c r="D143" t="s">
-        <v>503</v>
+        <v>192</v>
       </c>
       <c r="E143" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="F143" t="s">
-        <v>503</v>
+        <v>192</v>
       </c>
       <c r="G143" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="H143" t="s">
-        <v>505</v>
+        <v>192</v>
       </c>
       <c r="I143" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="J143">
         <v>2</v>
@@ -8737,45 +8746,45 @@
         <v>21</v>
       </c>
       <c r="L143">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M143" t="s">
         <v>22</v>
       </c>
       <c r="N143" t="s">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="O143" t="s">
-        <v>501</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B144" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C144" t="s">
-        <v>508</v>
+        <v>86</v>
       </c>
       <c r="D144" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="E144" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="F144" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="G144" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="H144" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I144" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="J144">
         <v>2</v>
@@ -8784,45 +8793,45 @@
         <v>21</v>
       </c>
       <c r="L144">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M144" t="s">
         <v>22</v>
       </c>
       <c r="N144" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
       <c r="O144" t="s">
-        <v>512</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B145" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C145" t="s">
+        <v>507</v>
+      </c>
+      <c r="D145" t="s">
         <v>508</v>
       </c>
-      <c r="D145" t="s">
-        <v>515</v>
-      </c>
       <c r="E145" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="F145" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G145" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="H145" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="I145" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J145">
         <v>2</v>
@@ -8837,39 +8846,39 @@
         <v>22</v>
       </c>
       <c r="N145" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="O145" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="B146" t="s">
+        <v>512</v>
+      </c>
+      <c r="C146" t="s">
+        <v>513</v>
+      </c>
+      <c r="D146" t="s">
         <v>514</v>
       </c>
-      <c r="C146" t="s">
-        <v>508</v>
-      </c>
-      <c r="D146" t="s">
-        <v>520</v>
-      </c>
       <c r="E146" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="F146" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="G146" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="H146" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="I146" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="J146">
         <v>2</v>
@@ -8878,95 +8887,95 @@
         <v>21</v>
       </c>
       <c r="L146">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M146" t="s">
         <v>22</v>
       </c>
       <c r="N146" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="O146" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B147" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C147" t="s">
-        <v>525</v>
+        <v>226</v>
       </c>
       <c r="D147" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E147" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="F147" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="G147" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="H147" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="I147" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="J147">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K147" t="s">
         <v>21</v>
       </c>
       <c r="L147">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M147" t="s">
         <v>22</v>
       </c>
       <c r="N147" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="O147" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B148" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="C148" t="s">
-        <v>532</v>
+        <v>226</v>
       </c>
       <c r="D148" t="s">
-        <v>441</v>
+        <v>525</v>
       </c>
       <c r="E148" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="F148" t="s">
-        <v>441</v>
+        <v>525</v>
       </c>
       <c r="G148" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="H148" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="I148" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="J148">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K148" t="s">
         <v>21</v>
@@ -8975,42 +8984,42 @@
         <v>90</v>
       </c>
       <c r="M148" t="s">
-        <v>536</v>
+        <v>22</v>
       </c>
       <c r="N148" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="O148" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="B149" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="C149" t="s">
-        <v>540</v>
+        <v>226</v>
       </c>
       <c r="D149" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="E149" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="F149" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="G149" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="H149" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="I149" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="J149">
         <v>2</v>
@@ -9025,10 +9034,104 @@
         <v>22</v>
       </c>
       <c r="N149" t="s">
+        <v>528</v>
+      </c>
+      <c r="O149" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>533</v>
+      </c>
+      <c r="B150" t="s">
+        <v>534</v>
+      </c>
+      <c r="C150" t="s">
+        <v>535</v>
+      </c>
+      <c r="D150" t="s">
+        <v>536</v>
+      </c>
+      <c r="E150" t="s">
+        <v>537</v>
+      </c>
+      <c r="F150" t="s">
+        <v>536</v>
+      </c>
+      <c r="G150" t="s">
+        <v>537</v>
+      </c>
+      <c r="H150" t="s">
+        <v>538</v>
+      </c>
+      <c r="I150" t="s">
+        <v>539</v>
+      </c>
+      <c r="J150">
+        <v>16</v>
+      </c>
+      <c r="K150" t="s">
+        <v>21</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150" t="s">
+        <v>22</v>
+      </c>
+      <c r="N150" t="s">
+        <v>534</v>
+      </c>
+      <c r="O150" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>540</v>
+      </c>
+      <c r="B151" t="s">
+        <v>541</v>
+      </c>
+      <c r="C151" t="s">
+        <v>542</v>
+      </c>
+      <c r="D151" t="s">
+        <v>447</v>
+      </c>
+      <c r="E151" t="s">
+        <v>543</v>
+      </c>
+      <c r="F151" t="s">
+        <v>447</v>
+      </c>
+      <c r="G151" t="s">
+        <v>543</v>
+      </c>
+      <c r="H151" t="s">
         <v>544</v>
       </c>
-      <c r="O149" t="s">
-        <v>544</v>
+      <c r="I151" t="s">
+        <v>545</v>
+      </c>
+      <c r="J151">
+        <v>16</v>
+      </c>
+      <c r="K151" t="s">
+        <v>21</v>
+      </c>
+      <c r="L151">
+        <v>90</v>
+      </c>
+      <c r="M151" t="s">
+        <v>546</v>
+      </c>
+      <c r="N151" t="s">
+        <v>547</v>
+      </c>
+      <c r="O151" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>
